--- a/xlsx/hellforged-ru.xlsx
+++ b/xlsx/hellforged-ru.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Хорошо</t>
+          <t>ОК</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Мортензия вернулась, но её путь ещё не готов.
-Спасибо, что играли в демо. Она станет играбельной в одном из будущих обновлений.</t>
+Спасибо, что играете в демоверсию. Она станет доступна для игры в одном из будущих обновлений.</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>{abilityName} (Основная атака)</t>
+          <t>{abilityName} (основная атака)</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Отслеживается ({trackedAmount})</t>
+          <t>Отслеживаемые ({trackedAmount})</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Достижения открыты</t>
+          <t>Достижение получено</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Отслеживаемые достижения показываются в игре с прогрессом.\nМожно отслеживать до 3 достижений</t>
+          <t>Отслеживаемые достижения отображаются в игре с прогрессом.\nМожно отслеживать до 3 достижений</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Можно отслеживать максимум 3 достижения</t>
+          <t>Можно отслеживать не более 3 достижений</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Открыто</t>
+          <t>Разблокировано</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Открывает</t>
+          <t>Разблокирует</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ваши способности появляются во время забега из Святилища силы</t>
+          <t>Способности появляются в забеге из Святилища силы</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Этот предмет нельзя убрать, некоторые слоты всегда должны быть заполнены.</t>
+          <t>Этот предмет нельзя убрать: часть слотов всегда должна быть заполнена.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Ваши морфы появляются во время забега при повышении уровня</t>
+          <t>Морфы появляются в забеге при повышении уровня</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Ваши реликвии появляются во время забега из Сундуков с сокровищами</t>
+          <t>Реликвии появляются в забеге из сундуков с сокровищами</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Требует</t>
+          <t>Требуется</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (Наполнено)</t>
+          <t xml:space="preserve"> (Влитый)</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Возможный ролл</t>
+          <t>Возможное значение</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>от {minValue} до {maxValue}</t>
+          <t>{minValue} — {maxValue}</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Вознесение недоступно в плейтесте
-Мифическое снаряжение появится в Demo</t>
+Мифическое снаряжение появится в демо</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Недоступно в этом плейтесте
-Появится в demo</t>
+Появится в демо</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Требует легендарный предмет с главным аффиксом</t>
+          <t>Нужен легендарный предмет с крупным аффиксом</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Вознести</t>
+          <t>Вознесение</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Выберите архивную силу</t>
+          <t>Выбрать архивную силу</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Обычный/Редкий предмет с главным аффиксом</t>
+          <t>Обычный или редкий предмет с крупным аффиксом</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Усилить</t>
+          <t>Усиление</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Наполнить</t>
+          <t>Влить</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Наполнить свойства</t>
+          <t>Влить свойства</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Наполнить</t>
+          <t>Вливание</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>&lt;2&gt;Предложите&lt;/2&gt; накопленный хаос, &lt;2&gt;чтобы призвать&lt;/2&gt; босса</t>
+          <t>&lt;2&gt;Поднесите&lt;/2&gt; накопленный хаос, &lt;2&gt;чтобы призвать&lt;/2&gt; босса</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Собирайте Эссенцию Тени, чтобы получить</t>
+          <t>Соберите эссенцию Тени, чтобы получить</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Завершите за {seconds} секунд</t>
+          <t>Завершите за {seconds} с</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Детали</t>
+          <t>Подробности</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Детали</t>
+          <t>Подробности</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Детали</t>
+          <t>Подробности</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Автоматическое</t>
+          <t>Авто</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Ручное</t>
+          <t>Вручную</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Тяжёлая</t>
+          <t>Сложно</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Нормальная</t>
+          <t>Обычная</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>&lt;2&gt;Потратьте&lt;/2&gt; свой &lt;2&gt;хаос&lt;/2&gt;, чтобы &lt;2&gt;повысить награды&lt;/2&gt; за большую сложность</t>
+          <t>&lt;2&gt;Потратьте&lt;/2&gt; &lt;2&gt;хаос&lt;/2&gt;, чтобы &lt;2&gt;повысить награды&lt;/2&gt; за рост сложности</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Извлечённое</t>
+          <t>Извлечено</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Силы забега</t>
+          <t>Усиления забега</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Не задано</t>
+          <t>Не определено</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Не задано</t>
+          <t>Не определено</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Скорость</t>
+          <t>Скорость передвижения</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Эффекты</t>
+          <t>Статус-эффекты</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Не задано</t>
+          <t>Не определено</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Число отскоков</t>
+          <t>Кол-во отскоков</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов</t>
+          <t>Кол-во снарядов</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Главный</t>
+          <t>Крупный</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Эпический\nреролл</t>
+          <t>Эпическая\nперекрутка</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Сброс</t>
+          <t>Сбросить</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Фокус-трейты</t>
+          <t>Черты сосредоточения</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Фокус-трейт</t>
+          <t>Черта сосредоточения</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Общий ур. предметов</t>
+          <t>Сумм. ур. предметов</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Бежать к Обелиску</t>
+          <t>Бегство к Обелиску</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Извлечённые предметы</t>
+          <t>Вынесенные предметы</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Извлечённые ресурсы</t>
+          <t>Вынесенные ресурсы</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Глобальная</t>
+          <t>Глобальный</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Пожалуйста, выберите другое имя.</t>
+          <t>Выберите другое имя.</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Имя должно быть не длиннее {maxLength} символов.</t>
+          <t>Имя должно содержать не более {maxLength} символов.</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Имя должно быть не короче {minLength} символов.</t>
+          <t>Имя должно содержать не менее {minLength} символов.</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Пока без ранга</t>
+          <t>Без ранга</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>{value}д</t>
+          <t>{value} д</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>{value}ч</t>
+          <t>{value} ч</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>{value}м</t>
+          <t>{value} мин</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>В топ {0}% игроков</t>
+          <t>В топ-{0}% игроков</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Продолжить или начать новый профиль</t>
+          <t>Продолжите или создайте новый профиль</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Ранги карт</t>
+          <t>Уровни карт</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Подсклеп</t>
+          <t>Подземный склеп</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Эволюция сейчас</t>
+          <t>Развить сейчас</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Выйти</t>
+          <t>Уйти</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Разблокировано</t>
+          <t>разблокировано</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Теперь доступен &lt;1&gt;Арсенал&lt;/1&gt;. Откройте его, чтобы изучать новые силы и создавать свои билды.</t>
+          <t>&lt;1&gt;Арсенал&lt;/1&gt; теперь доступен. Откройте его, чтобы изучать новые силы и создавать свои сборки.</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Добавляйте сюда способности и реликвии, чтобы решить, что может появиться в забеге.
+          <t>Добавляйте сюда способности и реликвии, чтобы решить, что может выпасть в забеге.
 Во время забега &lt;1&gt;святилища&lt;/1&gt; и &lt;1&gt;сундуки&lt;/1&gt; предлагают лишь случайный выбор из того, что вы добавили.</t>
         </is>
       </c>
@@ -6027,7 +6027,7 @@
       <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Изучайте новые способности и покупайте реликвии.
-Активные силы &lt;1&gt;имеют шанс&lt;/1&gt; появиться во время забегов.
+Активные силы &lt;1&gt;имеют шанс&lt;/1&gt; появиться в ваших забегах.
 Арсенал — это место, где вы формируете свой стиль игры.</t>
         </is>
       </c>
@@ -6073,8 +6073,8 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Пока &lt;1&gt;Обелиск&lt;/1&gt; открыт, вы можете запечатывать &lt;1&gt;Разломы&lt;/1&gt; за &lt;1&gt;Хаос&lt;/1&gt; и &lt;1&gt;Очки&lt;/1&gt;. Запечатывание также продлевает таймер.
-Когда таймер истечёт, начнётся &lt;1&gt;Коллапс&lt;/1&gt;, и смертоносная порча медленно поглотит карту.</t>
+          <t>Пока &lt;1&gt;Обелиск&lt;/1&gt; открыт, вы можете запечатывать &lt;1&gt;Разломы&lt;/1&gt; ради &lt;1&gt;Хаоса&lt;/1&gt; и &lt;1&gt;Очков&lt;/1&gt;. Запечатывание также продлевает таймер.
+Когда таймер истекает, начинается &lt;1&gt;Коллапс&lt;/1&gt;, и смертоносная порча медленно поглощает карту.</t>
         </is>
       </c>
     </row>
@@ -6119,8 +6119,8 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Этот портал позволяет покинуть забег раньше времени и сохранить добычу.
-Вы можете вернуться сюда позже, чтобы извлечь её.</t>
+          <t>Этот портал позволяет покинуть забег раньше и сохранить добычу.
+Вы можете вернуться сюда позже, чтобы эвакуироваться.</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Первые &lt;1&gt;3 предмета добычи&lt;/1&gt; защищаются автоматически.
-Любая лишняя добыча незащищена и будет потеряна, если вы погибнете.</t>
+Любая лишняя добыча не защищена и будет потеряна, если вы погибнете.</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>&lt;1&gt;Обелиск&lt;/1&gt; теперь заряжен: &lt;1&gt;Бегите&lt;/1&gt;, чтобы завершить экспедицию.</t>
+          <t>&lt;1&gt;Обелиск&lt;/1&gt; заряжен: &lt;1&gt;сбегите&lt;/1&gt;, чтобы завершить Экспедицию.</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>У вас новый предмет. Откройте инвентарь и экипируйте его, чтобы стать сильнее.</t>
+          <t>У вас новый предмет. Откройте инвентарь и наденьте его, чтобы стать сильнее.</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Боевой журнал</t>
+          <t>Боевой лог</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Ведущая рука</t>
+          <t>Режим руки</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Показывать цифры урона</t>
+          <t>Показывать числа урона</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Звуки</t>
+          <t>Звук. эффекты</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Верт. синхр.</t>
+          <t>Верт. синхронизация</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>ВЫХОД</t>
+          <t>Выход</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Трейт — {prerequisiteName}</t>
+          <t>Черта — {prerequisiteName}</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Трейт основной атаки</t>
+          <t>Черта основной атаки</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Трейт</t>
+          <t>Черта</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Взаимоисключаемо с другими специализациями</t>
+          <t>Несовместимо с другими специализациями</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Спасибо за игру и добавьте Hellforged в список желаемого в Steam</t>
+          <t>Спасибо за игру! Добавьте Hellforged в список желаемого в Steam</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Характеристики, заданные вашим текущим билдом Арсенала. Это оптимальные характеристики, которые стоит искать на снаряжении, чтобы лучше всего масштабировать ваши способности и реликвии.</t>
+          <t>Характеристики, определяемые текущей сборкой Арсенала. Это оптимальные характеристики, которые стоит искать на снаряжении, чтобы лучше всего усиливать способности и реликвии.</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Легендарные</t>
+          <t>Легендарки</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Трейты</t>
+          <t>Черты</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Создать новое сохранение</t>
+          <t>Создать сохранение</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Вы уверены, что хотите удалить сохранение в слоте {slotId}?</t>
+          <t>Удалить сохранение в слоте {slotId}?</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Сохранение игры (нет файла)</t>
+          <t>Сохранение (нет файла)</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Вся ваша добыча теперь защищена и не будет потеряна при смерти</t>
+          <t>Вся ваша добыча защищена и не будет потеряна при смерти</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Левая рука</t>
+          <t>Левша</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Правая рука</t>
+          <t>Правша</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Максимальная производительность</t>
+          <t>Ультрапроизводительность</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Вступайте в наш Discord</t>
+          <t>Вступить в наш Discord</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает частоту срабатывания ваших способностей</t>
+          <t>Повышает частоту срабатывания способностей</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон, наносимый способностями. Основная атака не масштабируется от этого значения.</t>
+          <t>Повышает урон, наносимый способностями. Основная атака не масштабируется от этого значения.</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает весь наносимый вами урон, включая основную атаку, способности, перегрузку и эффекты.</t>
+          <t>Повышает весь наносимый урон, включая основную атаку, способности, Перегрузку и статус-эффекты.</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает размер площадных способностей, позволяя им поражать врагов на большей территории.</t>
+          <t>Увеличивает размер площадных способностей, позволяя поражать врагов на большей площади.</t>
         </is>
       </c>
     </row>
@@ -8522,8 +8522,8 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>&lt;1&gt;Броня&lt;/1&gt; снижает физический урон, наносимый вам врагами. Максимально эффективная броня ограничена значением &lt;1&gt;{maximumArmor}&lt;/1&gt;
-Снижение не может превышать &lt;1&gt;{armorCap}&lt;/1&gt;. Предел снижения можно повысить в Вечном Древе.
+          <t>&lt;1&gt;Броня&lt;/1&gt; снижает физический урон, наносимый врагами. Максимальная эффективная броня ограничена значением &lt;1&gt;{maximumArmor}&lt;/1&gt;
+Снижение не может превысить &lt;1&gt;{armorCap}&lt;/1&gt;. Предел снижения можно повысить в Вечном Древе.
 Текущее снижение: &lt;1&gt;{currentReduction}&lt;/1&gt;</t>
         </is>
       </c>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Максимальное снижение физического урона, которого может достичь броня. Повышение этого значения позволяет броне защищать вас сверх текущего предела.</t>
+          <t>Максимальное снижение физического урона, которого может достичь броня. Повышение этого предела позволяет броне защищать сверх текущего лимита.</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Заставляет эффекты кровотечения наносить больше урона. Добавляется к урону атаки до расчёта процента урона кровотечения и бонусов урона.</t>
+          <t>Заставляет эффекты кровотечения наносить больше урона. Добавляется к урону атаки до расчёта процента урона кровотечения и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Заставляет эффекты горения наносить больше урона. Добавляется к урону атаки до расчёта процента урона горения и бонусов урона.</t>
+          <t>Заставляет эффекты горения наносить больше урона. Добавляется к урону атаки до расчёта процента урона горения и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Заставляет холодные способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов урона.</t>
+          <t>Заставляет холодные способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>&lt;1&gt;Урон атаки&lt;/1&gt; — это ключевая характеристика, от которой масштабируются все ваши атаки и способности, образуя основу для вашего общего урона.</t>
+          <t>&lt;1&gt;Урон атаки&lt;/1&gt; — основная характеристика, от которой масштабируются все атаки и способности, формируя фундамент общего урона.</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Заставляет огненные способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов урона.</t>
+          <t>Заставляет огненные способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Заставляет способности молнии бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов урона.</t>
+          <t>Заставляет способности молнии бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Заставляет мистические способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов урона.</t>
+          <t>Заставляет мистические способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Усиливает некротические способности. Добавляется к урону атаки до расчёта процента урона способности и бонусов урона.</t>
+          <t>Заставляет некротические способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Добавляет фиксированный урон способностям перегрузки до применения бонусов урона перегрузки.</t>
+          <t>Добавляет фиксированный урон способностям Перегрузки до применения бонусов к урону Перегрузки.</t>
         </is>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Базовый урон перегрузки</t>
+          <t>Базовый урон Перегрузки</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Усиливает физические способности. Добавляется к урону атаки до расчёта процента урона способности и бонусов урона.</t>
+          <t>Заставляет физические способности бить сильнее. Добавляется к урону атаки до расчёта процента урона способностей и бонусов к урону.</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Продлевает эффекты кровотечения. Более долгое кровотечение может нанести больше суммарного урона, пока эффект тикает.</t>
+          <t>Заставляет эффекты кровотечения длиться дольше. Более долгое кровотечение может нанести больше суммарного урона, пока эффект продолжает тикать.</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Число отскоков</t>
+          <t>Кол-во отскоков</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Ядро</t>
+          <t>Основа</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Общее</t>
+          <t>Глобальные</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Эффекты</t>
+          <t>Статус-эффекты</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает золото, получаемое за награды челленджей.</t>
+          <t>Повышает золото, получаемое за награды испытаний.</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Бонус золота за челленджи</t>
+          <t>Бонус золота за испытания</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Цена в осколках Хаоса</t>
+          <t>Стоимость в осколках хаоса</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Снижает цену в золоте за запертые сундуки.</t>
+          <t>Снижает стоимость запертых сундуков в золоте.</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Снижение цены сундуков</t>
+          <t>Снижение стоимости сундуков</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает радиус сбора опыта и подбираемых предметов.</t>
+          <t>Увеличивает радиус сбора опыта и предметов.</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Снижение получаемого урона</t>
+          <t>Уменьшение получаемого урона</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает число рывков, которые можно накопить до перезарядки.</t>
+          <t>Увеличивает количество рывков, которые можно накопить до восстановления.</t>
         </is>
       </c>
     </row>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Время восстановления одного заряда рывка</t>
+          <t>Время восстановления 1 заряда рывка</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Снижение перезарядки рывка</t>
+          <t>Сокращение перезарядки рывка</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает скорость, с которой рывок переносит вас к цели.</t>
+          <t>Увеличивает скорость перемещения рывком к точке назначения.</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Стихийное сопротивление</t>
+          <t>Сопротивление стихиям</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон, наносимый элитным и боссовым врагам. Обычные враги не затрагиваются.</t>
+          <t>Увеличивает урон, наносимый элитным врагам и боссам. На обычных врагов не действует.</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Бонус урона по элитам и боссам</t>
+          <t>Бонус урона элите и боссам</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает золото, выпадающее с врагов. Складывается с приростом золота при сборе золота врагов.</t>
+          <t>Увеличивает количество золота, выпадающего с врагов. Складывается с Приростом золота при сборе золота с врагов.</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Бонус выпадения золота с врагов</t>
+          <t>Бонус золота с врагов</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Поглощает урон до здоровья и восстанавливается, когда вы избегаете ударов.</t>
+          <t>Поглощает урон до здоровья и восстанавливается при уклонении от попаданий.</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Процент максимального энергощита, восстанавливаемый каждую секунду во время перезарядки.</t>
+          <t>Процент от максимального энергощита, восстанавливаемый каждую секунду при перезарядке.</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>Восстановление энергощита</t>
+          <t>Скорость восстановления энергощита</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Максимальный шанс избежать прямого урона. Повышение этого предела позволяет шансу уклонения защищать вас сверх текущего предела.</t>
+          <t>Максимальный шанс избежать прямого урона. Повышение этого предела позволяет Шансу уклонения защищать сверх текущего лимита.</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       <c r="D438" s="2" t="inlineStr">
         <is>
           <t>Шанс избежать получения урона.
-Максимальный шанс уклонения ограничен &lt;1&gt;{evadeCap}&lt;/1&gt;</t>
+Максимальный шанс уклонения ограничен значением &lt;1&gt;{evadeCap}&lt;/1&gt;</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Бонус опыта</t>
+          <t>Бонус прироста опыта</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Это рекомендуемая характеристика для вашего билда Арсенала. Ищите её на снаряжении, чтобы стать сильнее.</t>
+          <t>Это рекомендуемая характеристика для вашей сборки Арсенала. Ищите её на снаряжении, чтобы стать сильнее.</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Бонус скорости при сборе</t>
+          <t>Бонус скорости сбора</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает золото, получаемое из большинства источников. Золото врагов использует и прирост золота, и бонус выпадения золота с врагов.</t>
+          <t>Увеличивает золото, получаемое из большинства источников. Золото с врагов учитывает и Прирост золота, и Бонус золота с врагов.</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>Лечение при повышении уровня</t>
+          <t>Исцеление при повышении уровня</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Поглощение удара (величина)</t>
+          <t>Величина поглощения удара</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>Поглощение удара (заряды)</t>
+          <t>Заряды поглощения ударов</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Интервал восстановления зарядов поглощения удара</t>
+          <t>Интервал восстановления зарядов поглощения ударов</t>
         </is>
       </c>
     </row>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает число вариантов легендарных сил, из которых можно выбирать.</t>
+          <t>Увеличивает количество вариантов Легендарной силы на выбор.</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>Выбор легендарных сил</t>
+          <t>Выбор легендарной силы</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>Сколько урона вы можете получить до гибели.</t>
+          <t>Сколько урона можно получить до гибели.</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Максимальное здоровье</t>
+          <t>Макс. здоровье</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>Время между каждым лечением регенерации здоровья. Меньшие значения лечат вас чаще.</t>
+          <t>Время между восстановлениями здоровья. Меньшие значения исцеляют чаще.</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>Перезарядка регена</t>
+          <t>Перезарядка регенерации здоровья</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Количество здоровья, восстанавливаемое каждые {regenCooldown}с</t>
+          <t>Количество здоровья, восстанавливаемое каждые {regenCooldown} с</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Восстановление здоровья</t>
+          <t>Величина регенерации здоровья</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>Число появлений запертых сундуков</t>
+          <t>Количество появляющихся запертых сундуков</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>Максимальное снижение магического урона, которого может достичь магическое сопротивление. Повышение этого предела позволяет магическому сопротивлению защищать вас сверх текущего предела.</t>
+          <t>Максимальное снижение магического урона, которого может достичь сопротивление магии. Повышение этого предела позволяет сопротивлению магии защищать сверх текущего лимита.</t>
         </is>
       </c>
     </row>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>Предел магического сопротивления</t>
+          <t>Предел сопротивления магии</t>
         </is>
       </c>
     </row>
@@ -11123,8 +11123,8 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>Снижение урона от всех магических источников, таких как вражеские огненные шары, области эффекта или некротические снаряды.
-Максимальное магическое сопротивление ограничено &lt;1&gt;{magicCap}&lt;/1&gt;</t>
+          <t>Снижение урона от всех магических источников: вражеских огненных шаров, областей действия или некротических снарядов.
+Максимальное сопротивление магии ограничено значением &lt;1&gt;{magicCap}&lt;/1&gt;</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>Магическое сопротивление</t>
+          <t>Сопротивление магии</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>Шанс наложить кровотечение при попадании основной атаки.</t>
+          <t>Шанс наложить Кровотечение при попадании основной атакой.</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>Шанс наложить порчу при попадании основной атаки.</t>
+          <t>Шанс наложить Порчу при попадании основной атакой.</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>Шанс наложить горение при попадании основной атаки.</t>
+          <t>Шанс наложить Горение при попадании основной атакой.</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>Шанс наложить охлаждение при попадании основной атаки.</t>
+          <t>Шанс наложить Озноб при попадании основной атакой.</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Шанс охлаждения от основной атаки</t>
+          <t>Шанс озноба от основной атаки</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>Как быстро движется ваш герой</t>
+          <t>Как быстро перемещается герой</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Как часто можно использовать способность перегрузки</t>
+          <t>Как часто можно использовать способность Перегрузка</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>Перезарядка перегрузки</t>
+          <t>Перезарядка Перегрузки</t>
         </is>
       </c>
     </row>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон, наносимый способностями перегрузки. Масштабирует урон перегрузки после расчёта её базового урона.</t>
+          <t>Увеличивает урон от способностей Перегрузки. Этот бонус масштабирует урон Перегрузки после расчёта её базового урона.</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Бонус урона перегрузки</t>
+          <t>Бонус урона Перегрузки</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>Восстановление перегрузки</t>
+          <t>Восстановление Перегрузки</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>Сверхздоровье (%)</t>
+          <t>Процент сверхздоровья</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Добавляет больше снарядов способностям на основе снарядов. Бонус процентный, поэтому +100% превращает 1 снаряд в 2.</t>
+          <t>Добавляет снаряды способностям, основанным на снарядах. Бонус процентный, поэтому +100% превращает 1 снаряд в 2.</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов (бонус)</t>
+          <t>Бонус количества снарядов</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов</t>
+          <t>Кол-во снарядов</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>Дальность снаряда (бонус)</t>
+          <t>Бонус дальности снарядов</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>Дальность снаряда</t>
+          <t>Дальность снарядов</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>Скорость снаряда (бонус)</t>
+          <t>Бонус скорости снарядов</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>Скорость снаряда</t>
+          <t>Скорость снарядов</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>Бонус радиуса захвата рунного камня</t>
+          <t>Бонус радиуса захвата рунных камней</t>
         </is>
       </c>
     </row>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>Бонус скорости захвата рунного камня</t>
+          <t>Бонус скорости захвата рунных камней</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>Слоты защиты</t>
+          <t>Защищённые слоты</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>Бонус радиуса захвата сигила</t>
+          <t>Бонус радиуса захвата сигилов</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>Бонус скорости захвата сигила</t>
+          <t>Бонус скорости захвата сигилов</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>Число появлений сигилов</t>
+          <t>Количество появляющихся сигилов</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>Золото, с которым вы начинаете каждый забег.</t>
+          <t>Золото, с которым начинается каждый забег.</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Шанс наложения эффекта</t>
+          <t>Шанс наложения статуса</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон, наносимый всеми статусными эффектами, такими как горение или кровотечение.</t>
+          <t>Увеличивает урон от всех статус-эффектов, таких как Горение или Кровотечение.</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>Бонус урона эффектов</t>
+          <t>Бонус урона статус-эффектов</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Бонус длительности эффектов</t>
+          <t>Бонус длительности статус-эффектов</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>Макс. стаки эффекта</t>
+          <t>Макс. зарядов статус-эффекта</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Стаки эффекта</t>
+          <t>Заряды статус-эффекта</t>
         </is>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>Отражает {percentValue}% вашего урона атаки (сейчас {currentDamage}) обратно атакующим при попадании. Шипы масштабируются со всеми бонусами урона, как любой другой урон.</t>
+          <t>Отражает {percentValue}% урона атаки (сейчас {currentDamage}) обратно атакующим при попадании. Шипы масштабируются всеми бонусами урона, как и любой другой урон.</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>(Складываемый)</t>
+          <t>(Аддитивно)</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Базовое:</t>
+          <t>База:</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>Итоговое:</t>
+          <t>Итог:</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Увеличено за счёт {linkedStatName}</t>
+          <t>Увеличено {linkedStatName}</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Изменено за счёт {linkedStatName}</t>
+          <t>Изменено {linkedStatName}</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>Снижено за счёт {linkedStatName}</t>
+          <t>Уменьшено {linkedStatName}</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12620,7 @@
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>(Множительный)</t>
+          <t>(Мультипликативно)</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>Уровень предмета в добыче</t>
+          <t>Уровень выпадающих предметов</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>Соберите эссенцию, чтобы призвать &lt;1&gt;Тень&lt;/1&gt;</t>
+          <t>Соберите эссенцию, чтобы призвать Тень</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>Найдите &lt;1&gt;Тень&lt;/1&gt;, чтобы выбрать морф способности</t>
+          <t>Найдите Тень, чтобы выбрать морф способности</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>Применить перегрузку</t>
+          <t>Использовать Перегрузку</t>
         </is>
       </c>
     </row>
@@ -13017,8 +13017,8 @@
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>Мы — небольшая инди-команда, создающая Hellforged вокруг простой идеи: скорость и хаос horde-сурвайвала с лутом, билдами и долгосрочным развитием, которые мы любим в ARPG.
-Когда у вас будет возможность поиграть, пожалуйста, заполните нашу форму обратной связи или присоединяйтесь к нашему Discord, чтобы поделиться мыслями напрямую с командой.</t>
+          <t>Мы — небольшая инди-команда, создающая Hellforged вокруг простой идеи: скорость и хаос horde-survivor в сочетании с добычей, сборками и долгосрочной прогрессией, которые мы так любим в ARPG.
+Когда наиграетесь, заполните, пожалуйста, нашу форму отзывов или вступите в наш Discord, чтобы поделиться мыслями напрямую с командой.</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Автоатака выключена</t>
+          <t>Автоатака отключена</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Войти в {mapName}</t>
+          <t>Войти: {mapName}</t>
         </is>
       </c>
     </row>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Челлендж &lt;b&gt;{challengeName}&lt;/b&gt; принят</t>
+          <t>Принято испытание &lt;b&gt;{challengeName}&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>{challengeName}: завершён</t>
+          <t>{challengeName}: испытание пройдено</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Пилоны вытягивают здоровье, пока вы находитесь в их радиусе</t>
+          <t>Пилоны вытягивают здоровье, пока вы стоите в их радиусе</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>{challengeName}: провален</t>
+          <t>{challengeName}: испытание провалено</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Недостаточно хаоса для начала челленджа. Нужно {chaosCost} хаоса.</t>
+          <t>Недостаточно хаоса для начала испытания. Нужно {chaosCost} хаоса.</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Челлендж запечатан</t>
+          <t>Испытание запечатано</t>
         </is>
       </c>
     </row>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Принять челлендж</t>
+          <t>Принять испытание</t>
         </is>
       </c>
     </row>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Вы получили {damageAmount} ед. урона ({damageType})</t>
+          <t>Вы получили {damageAmount} {damageType} урона</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>{sourceName} нанёс вам {damageAmount} ед. урона ({damageType})</t>
+          <t>{sourceName} нанёс вам {damageAmount} {damageType} урона</t>
         </is>
       </c>
     </row>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Поглощение</t>
+          <t>Поглощено</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Сложность повышена</t>
+          <t>Повышение сложности</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Орды врагов становятся сильнее</t>
+          <t>Орды врагов набирают силу</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>+{scorePercentageIncrease}% к получаемым очкам</t>
+          <t>+{scorePercentageIncrease}% к приросту очков</t>
         </is>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Защищайте портал, пока он заряжается, чтобы вернуться в Лагерь.\n&lt;1&gt;Вся полученная добыча сохраняется.&lt;/1&gt;</t>
+          <t>Защищайте портал, пока он заряжается, чтобы вернуться в Лагерь.\n&lt;1&gt;Вся добытая добыча остаётся при вас.&lt;/1&gt;</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Бежать в Лагерь?</t>
+          <t>Сбежать в Лагерь?</t>
         </is>
       </c>
     </row>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Бежать в Лагерь</t>
+          <t>Сбежать в Лагерь</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Уйдите через обелиск или запечатайте разломы</t>
+          <t>Сбегите через обелиск или запечатайте разломы</t>
         </is>
       </c>
     </row>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Выживайте, пока обелиск заряжается</t>
+          <t>Выживайте, пока заряжается обелиск</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Взаимодействие</t>
+          <t>Взаимодействовать</t>
         </is>
       </c>
     </row>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Орды врагов становятся сильнее</t>
+          <t>Орды врагов набирают силу</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Морф &lt;1&gt;{morphName}&lt;/1&gt; эволюционировал и активен</t>
+          <t>Морф &lt;1&gt;{morphName}&lt;/1&gt; теперь развит и активен</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Говорить</t>
+          <t>Поговорить</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Зарядится через {0}</t>
+          <t>Зарядка через {0}</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Коллапс завершился!</t>
+          <t>Коллапс завершён!</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Трейт — {powerupName}</t>
+          <t>Черта — {powerupName}</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>{scoreModifier} к очкам</t>
+          <t>Бонус к очкам {scoreModifier}</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>+{seconds}с получено</t>
+          <t>+{seconds} с получено</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>{shrineName} появилось</t>
+          <t>Появилось: {shrineName}</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Мы нашли древние врата, наполовину занесённые землёй и забытые. Никто не знал, куда они ведут.</t>
+          <t>Мы нашли древние врата, полузасыпанные и забытые. Никто не знал, куда они ведут.</t>
         </is>
       </c>
     </row>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Я перешёл вместе с экспедицией. Наши карты стали бесполезны, едва мы ступили за порог.</t>
+          <t>Я отправилась с экспедицией. Наши карты стали бесполезны, едва мы шагнули за порог.</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Этот мир с первого вздоха ощущался неправильным. А потом врата запечатались за нашими спинами.</t>
+          <t>Этот мир ощущался неправильным с первого вздоха. А потом врата запечатались за нашими спинами.</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Той ночью искажённые чудовища обрушились на наш лагерь. Следом пришли демоны — забрать то, что осталось.</t>
+          <t>Той ночью на лагерь обрушились извращённые твари. Следом пришли демоны — забрать то, что осталось.</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Я очнулся один в склепе, погребённый под мёртвыми.</t>
+          <t>Я очнулась одна в склепе, погребённая под мёртвыми.</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Преклони колени в моём склепе — или будешь запечатан под ним.</t>
+          <t>Преклони колени в моём склепе — или будешь замурован под ним.</t>
         </is>
       </c>
     </row>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>В этой гробнице ещё найдётся место для одного.</t>
+          <t>В этой гробнице найдётся место ещё для одного.</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Проходят века, а ваше племя всё возвращается.</t>
+          <t>Проходят века, а твой род всё возвращается.</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Я веду заметки. В основном чтобы доказать, что мы тут не все спятили.</t>
+          <t>Я веду записи. Главным образом чтобы доказать, что мы не все спятили.</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Уже вернулся? Видать, этому миру нравится тебя жевать.</t>
+          <t>Уже вернулся? Видно, этому миру нравится тебя пожёвывать.</t>
         </is>
       </c>
     </row>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>А, ты жив. Сам вытащил тебя из того склепа — теперь ты мне должен.</t>
+          <t>А, ты жив. Сам вытащил тебя из того склепа — так что ты мне должен.</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Портал запечатался после нападения. Но всё ещё гудит — сходи глянь.</t>
+          <t>Портал запечатался после нападения. Но всё ещё гудит — сходи, глянь.</t>
         </is>
       </c>
     </row>
@@ -15500,7 +15500,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Из тьмы выходит истинный ужас. Я не преклоню колени.</t>
+          <t>Из тьмы выступает истинный ужас. Я не преклоню колен.</t>
         </is>
       </c>
     </row>
@@ -15544,7 +15544,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Путь наружу открыт. Теперь у жадности есть таймер.</t>
+          <t>Путь наружу открыт. У жадности теперь есть таймер.</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Можно уйти сейчас — или сперва захватить разломы.</t>
+          <t>Можно уйти сейчас — или сперва запечатать разломы.</t>
         </is>
       </c>
     </row>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Обелиск заряжен, отыщем выход.</t>
+          <t>Обелиск заряжен, пора найти путь наружу.</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Хаос ради награды… и сила — моим врагам.</t>
+          <t>Хаос в награду… и сила моим врагам.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Это сияние... реликвия истинной силы.</t>
+          <t>Это сияние… реликвия истинной силы.</t>
         </is>
       </c>
     </row>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Древняя сила вновь нашла путь в мои руки.</t>
+          <t>Древняя сила вновь обрела дорогу в мои руки.</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Это место рушится, мне пора уходить.</t>
+          <t>Это место рушится, нужно уходить.</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Задержись подольше — и тьма поглотит меня целиком.</t>
+          <t>Задержусь дольше — и тьма поглотит меня целиком.</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Послужит, пока не подвернётся что получше.</t>
+          <t>Послужит, пока не подвернётся что-то получше.</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Работа не из лучших, но толк есть.</t>
+          <t>Не тонкая работа, но польза есть.</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Вот это стоит взять с собой.</t>
+          <t>Вот это стоит унести с собой.</t>
         </is>
       </c>
     </row>
@@ -15874,7 +15874,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Тот, кто это сделал, знал своё дело.</t>
+          <t>Тот, кто это создал, знал своё дело.</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Вещь покрепче. Послужит нам неплохо.</t>
+          <t>Вещь покрепче. Послужит нам как надо.</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Лучше большинства того, что оставляет это место.</t>
+          <t>Лучше, чем почти всё, что оставляет это место.</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Эта вещь побывала в бою и уцелела. Хорошо.</t>
+          <t>Это побывало в бою и уцелело. Хорошо.</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>В этой вещи есть история — и не вся она мертва.</t>
+          <t>В этой вещи есть история, и не вся она мертва.</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Это создано не только для убийства.</t>
+          <t>Это создавали не только ради убийства.</t>
         </is>
       </c>
     </row>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Этот клинок повидал панику. С паникой я работать умею.</t>
+          <t>Этот клинок знавал панику. С паникой я работать умею.</t>
         </is>
       </c>
     </row>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Хорошее снаряжение не спасает глупцов. Лишь даёт им чуть больше времени.</t>
+          <t>Хорошее снаряжение не спасает глупцов. Лишь даёт им дольше протянуть.</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Твоя броня держится. В основном.</t>
+          <t>Твоя броня держится. По большей части.</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Выглядишь помятым. Броня — ещё хуже.</t>
+          <t>Выглядишь помятым. Броня выглядит хуже.</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Не глазей. Воскрешение редко бывает к лицу.</t>
+          <t>Не пялься. Воскрешение редко бывает к лицу.</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Лагерь становится громче, когда ты выживаешь.</t>
+          <t>Лагерь шумит громче, когда ты выживаешь.</t>
         </is>
       </c>
     </row>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Мёртвые никогда не были твоими, чтобы хоронить их.</t>
+          <t>Хоронить мёртвых было не в твоей власти.</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Живые не заходили так далеко уже целые эпохи.</t>
+          <t>Живые не забирались так далеко уже целые эпохи.</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Ты не первый, кто вернулся изменённым.</t>
+          <t>Ты не первый, кто возвращается изменённым.</t>
         </is>
       </c>
     </row>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Я видела, что случилось. Твои люди — схвачены, перебиты. Я не могла вмешаться.</t>
+          <t>Я видела, что произошло. Твой народ — захвачен, перебит. Я не могла вмешаться.</t>
         </is>
       </c>
     </row>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Эльфийка. Маг. Её утащили глубже. Жива ли она ещё — сказать не могу.</t>
+          <t>Эльфийка. Маг. Утащена глубже. Жива ли она ещё — сказать не могу.</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Я могу помочь придать форму твоим силам, Паладин.</t>
+          <t>Я могу помочь придать форму твоим силам, паладин.</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Я помню всё, Торен...</t>
+          <t>Я помню всё, Торен…</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Некоторых увели живыми — возможно, ещё есть шанс их отыскать.</t>
+          <t>Кого-то забрали живыми — возможно, ещё есть шанс их найти.</t>
         </is>
       </c>
     </row>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Ты всё ещё жив. Поразительно.</t>
+          <t>Ты ещё жив. Поразительно.</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Я видела, как забирали твоё племя. Никто не ушёл.</t>
+          <t>Я видела, как забирали твой род. Никто не ушёл.</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Твоё тело может пасть, но душа ещё не перешла грань. Останься со мной.</t>
+          <t>Твоё тело может пасть, но твоя душа ещё не перешла черту. Останься со мной.</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Не здесь. Не так. Я принесу твою душу к огню.</t>
+          <t>Не здесь. Не так. Я отнесу твою душу к огню.</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Истёртая железная куртка</t>
+          <t>Поношенный железный панцирь</t>
         </is>
       </c>
     </row>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Латный хауберк в вмятинах</t>
+          <t>Помятый латный хауберк</t>
         </is>
       </c>
     </row>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Грубая стальная безрукавка</t>
+          <t>Грубый стальной доспех</t>
         </is>
       </c>
     </row>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Обветренная кольчуга</t>
+          <t>Видавшая виды кольчуга</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Нагрудный щиток в боевых шрамах</t>
+          <t>Иссечённый в боях нагрудник</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Окованная железом боевая безрукавка</t>
+          <t>Окованный железом боевой панцирь</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Доспешная туника в пятнах ржавчины</t>
+          <t>Тронутая ржавчиной броневая туника</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17148,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Вечная нагрудная пластина крепости</t>
+          <t>Вечный нагрудник-вал</t>
         </is>
       </c>
     </row>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Вечный авангардный хауберк</t>
+          <t>Вечный хауберк авангарда</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Оплот, выкованный драконом</t>
+          <t>Драконокованый оплот</t>
         </is>
       </c>
     </row>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Эгида предков</t>
+          <t>Эгида предка</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Бригантина из железной шкуры</t>
+          <t>Железношкурая бригантина</t>
         </is>
       </c>
     </row>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Боевые латы в медвежьей шкуре</t>
+          <t>Медвежьи боевые латы</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Каменная стражническая кираса</t>
+          <t>Каменностражная кираса</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17368,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Морозный ламелляр</t>
+          <t>Морозношкурый ламелляр</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Нагрудная пластина крепости</t>
+          <t>Нагрудник-вал</t>
         </is>
       </c>
     </row>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Хауберк, выкованный в углях</t>
+          <t>Угольнокованый хауберк</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Истёртая мантия послушника</t>
+          <t>Поношенная роба послушника</t>
         </is>
       </c>
     </row>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанное мистическое облачение</t>
+          <t>Истрёпанное мистическое облачение</t>
         </is>
       </c>
     </row>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Запылённый плащ странника</t>
+          <t>Запылённое одеяние странника</t>
         </is>
       </c>
     </row>
@@ -17566,7 +17566,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Протёртая до нитей ряса ученика</t>
+          <t>Ветхая ряса ученика</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Потёртый наряд пилигрима</t>
+          <t>Потёртое одеяние пилигрима</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Простая безрукавка кочевника</t>
+          <t>Простой панцирь кочевника</t>
         </is>
       </c>
     </row>
@@ -17632,7 +17632,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Выцветшее ритуальное сюрко</t>
+          <t>Выцветший ритуальный сюрко</t>
         </is>
       </c>
     </row>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Адово-тканое одеяние архимага</t>
+          <t>Сотканное в аду одеяние архимага</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Мантия чарослома драконьей души</t>
+          <t>Роба чароплётства драконьей души</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Облачение иерофанта теневого огня</t>
+          <t>Облачение иерофанта теневого пламени</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Угольно-благословлённое сюрко заклинателя</t>
+          <t>Сюрко заклинателя, благословлённый углём</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Пепельный чародейский наряд</t>
+          <t>Колдовское одеяние пепельного шторма</t>
         </is>
       </c>
     </row>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Роковая мантия рунотворца</t>
+          <t>Мантия рунотворца песни рока</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Мантия провидца, тронутая рунами</t>
+          <t>Роба провидца, тронутая рунами</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Облачение аркан из тлеющего шёлка</t>
+          <t>Облачение тайн из угольного шёлка</t>
         </is>
       </c>
     </row>
@@ -17874,7 +17874,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Туника адепта, сотканная из духа</t>
+          <t>Туника адепта, тканная духом</t>
         </is>
       </c>
     </row>
@@ -17896,7 +17896,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Мистическая ряса ночной вуали</t>
+          <t>Мистическая ряса завесы ночи</t>
         </is>
       </c>
     </row>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Проклятое сюрко послушника</t>
+          <t>Сюрко послушника, скованный порчей</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Грозовой плащ чародея</t>
+          <t>Кафтан чародея из нити бури</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Пепельное одеяние чернокнижника</t>
+          <t>Одеяние чернокнижника, тканное пеплом</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Наряд мудреца, связанного тенью</t>
+          <t>Одеяние мудреца, скованного тенью</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Обветренная безрукавка разведчика</t>
+          <t>Видавший виды панцирь разведчика</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Грубо сработанная туника охотника</t>
+          <t>Грубо сшитая туника охотника</t>
         </is>
       </c>
     </row>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Стёганый хауберк дорожной стражи</t>
+          <t>Стёганый хауберк дорожного стража</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Выцветшее сюрко авангарда</t>
+          <t>Выцветший сюрко авангарда</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанная нагрудная обмотка скитальца</t>
+          <t>Истрёпанная нагрудная обмотка скитальца</t>
         </is>
       </c>
     </row>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Адокованная кираса крепости</t>
+          <t>Адокованная кираса-вал</t>
         </is>
       </c>
     </row>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Роковые латы из драконьей чешуи</t>
+          <t>Латы рока из драконьей чешуи</t>
         </is>
       </c>
     </row>
@@ -18226,7 +18226,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Тлеющая безрукавка стража</t>
+          <t>Панцирь стража, объятый угольями</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Властелинский хауберк погибели теней</t>
+          <t>Хауберк властелина погибели тьмы</t>
         </is>
       </c>
     </row>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Кроваво-огненный плащ джаггернаута</t>
+          <t>Кроваво-огненный кафтан джаггернаута</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Роковая стальная кольчуга авангарда</t>
+          <t>Кольчуга авангарда из роковой стали</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Рунный охранный плащ</t>
+          <t>Защитный кафтан, скованный рунами</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Кираса авангарда, выкованная в углях</t>
+          <t>Угольнокованая кираса авангарда</t>
         </is>
       </c>
     </row>
@@ -18424,7 +18424,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Боевая туника, меченная порчей</t>
+          <t>Боевая туника, меченая порчей</t>
         </is>
       </c>
     </row>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Грозовой хауберк охотника</t>
+          <t>Хауберк охотника, тканный бурей</t>
         </is>
       </c>
     </row>
@@ -18468,7 +18468,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Облачение мантии ночной стражи</t>
+          <t>Облачение-мантия стража ночи</t>
         </is>
       </c>
     </row>
@@ -18490,7 +18490,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Пепельная чешуйчатая безрукавка</t>
+          <t>Чешуйчатый панцирь, скованный пеплом</t>
         </is>
       </c>
     </row>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Теневая боевая безрукавка</t>
+          <t>Теневой латный боевой панцирь</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Обветренные латные сабатоны</t>
+          <t>Видавшие виды латные сабатоны</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Истёртые стальные ножные щитки</t>
+          <t>Поношенные стальные поножи</t>
         </is>
       </c>
     </row>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Прочные солдатские поножи</t>
+          <t>Крепкие солдатские поножи</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Грубо сработанные ножные латы</t>
+          <t>Грубо отлитые наголенники</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Сабатоны в боевых пятнах</t>
+          <t>Закопчённые в боях сабатоны</t>
         </is>
       </c>
     </row>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Поножи титанова щита</t>
+          <t>Поножи щита титана</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Грозовые сабатоны сокрушителя</t>
+          <t>Сабатоны сокрушителя бурь</t>
         </is>
       </c>
     </row>
@@ -18754,7 +18754,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Ножные латы, выкованные миром</t>
+          <t>Кованные миром поножи</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Ботинки колосса</t>
+          <t>Поступь колосса</t>
         </is>
       </c>
     </row>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Вечные авангардные поножи</t>
+          <t>Вечные поножи авангарда</t>
         </is>
       </c>
     </row>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Боевые сапоги вершины</t>
+          <t>Вершинные боевые сапоги</t>
         </is>
       </c>
     </row>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Сабатоны сокрушающей зари</t>
+          <t>Сабатоны рассветного удара</t>
         </is>
       </c>
     </row>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Шагатели, связанные клятвой</t>
+          <t>Шагоходы, связанные клятвой</t>
         </is>
       </c>
     </row>
@@ -18886,7 +18886,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Поножи железного хребта</t>
+          <t>Железнохребетные поножи</t>
         </is>
       </c>
     </row>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Сабатоны, выкованные шипами</t>
+          <t>Шипокованые сабатоны</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Шипастые набедренники</t>
+          <t>Шипостражные наголенники</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Теневые шипастые поножи</t>
+          <t>Теневошипые поножи</t>
         </is>
       </c>
     </row>
@@ -18974,7 +18974,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Стражные щитки крепости</t>
+          <t>Наголенники-вал</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Каменно-оперённые ботинки</t>
+          <t>Камнепёрая поступь</t>
         </is>
       </c>
     </row>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Истёртые сандалии послушника</t>
+          <t>Поношенные сандалии послушника</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанные мистические туфли</t>
+          <t>Истрёпанные мистические туфли</t>
         </is>
       </c>
     </row>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Протёртые до нитей шаги кочевника</t>
+          <t>Ветхая поступь кочевника</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Выцветшие ботинки искателя приключений</t>
+          <t>Выцветшая поступь искателя приключений</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Грубо сработанные мокасины следопыта</t>
+          <t>Грубо сшитые мокасины следопыта</t>
         </is>
       </c>
     </row>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Адокованные шагатели арканиста</t>
+          <t>Адокованные шагоходы арканиста</t>
         </is>
       </c>
     </row>
@@ -19260,7 +19260,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Роковые ходоки драконьей души</t>
+          <t>Погибельные ходоки драконьей души</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Властелинские поножи теневого огня</t>
+          <t>Поножи властелина теневого пламени</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Тлеющие сапоги чарошага</t>
+          <t>Заклинательные сапоги, скованные углём</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Серафические ботинки ночной вуали</t>
+          <t>Серафическая поступь завесы ночи</t>
         </is>
       </c>
     </row>
@@ -19348,7 +19348,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Пепельные сабатоны проклятого всадника</t>
+          <t>Сабатоны порчевого всадника пепельного шторма</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Бездонные ножные щитки бури</t>
+          <t>Бездонные наголенники бури</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19392,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Кроваво-огненные ботинки иерофанта</t>
+          <t>Кроваво-огненная поступь иерофанта</t>
         </is>
       </c>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Тлеющие шаги пилигрима</t>
+          <t>Поступь пилигрима из угольной нити</t>
         </is>
       </c>
     </row>
@@ -19458,7 +19458,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Ботинки искателя, сотканные из духа</t>
+          <t>Сапоги искателя, тканные духом</t>
         </is>
       </c>
     </row>
@@ -19480,7 +19480,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Быстроходы теневой вуали</t>
+          <t>Быстроходы теневой завесы</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Проклятые обмотки путепрокладчика</t>
+          <t>Обмотки путепрядца, скованные порчей</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Ботинки арканиста ночного ветра</t>
+          <t>Поступь арканиста ночного ветра</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Грозовые шагатели мистика</t>
+          <t>Мистические шагоходы из нити бури</t>
         </is>
       </c>
     </row>
@@ -19568,7 +19568,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Пепельные мокасины адепта</t>
+          <t>Мокасины адепта, тканные пеплом</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Истёртые кожаные обмотки</t>
+          <t>Поношенные кожаные обмотки</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Запылённые ботинки авангарда</t>
+          <t>Запылённая поступь авангарда</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Грубо сработанные сабатоны налётчика</t>
+          <t>Грубо сшитые сабатоны налётчика</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанные шаги скитальца</t>
+          <t>Истрёпанная поступь скитальца</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Закалённые сапоги дорожной стражи</t>
+          <t>Закалённые сапоги дорожного стража</t>
         </is>
       </c>
     </row>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Выцветшие ножные накладки пилигрима</t>
+          <t>Выцветшие башмаки пилигрима</t>
         </is>
       </c>
     </row>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Роковые шагатели из драконьей чешуи</t>
+          <t>Погибельные шагоходы из драконьей чешуи</t>
         </is>
       </c>
     </row>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Ботинки преследователя теневого огня</t>
+          <t>Поступь преследователя теневого пламени</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Тлеющие боевые сабатоны</t>
+          <t>Боевые сабатоны, скованные углём</t>
         </is>
       </c>
     </row>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Сумеречные серафические ботинки</t>
+          <t>Сумеречные серафические сапоги</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Топтатели джаггернаута пепельной бури</t>
+          <t>Топотуны джаггернаута пепельного шторма</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19898,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Бездонные ходоки часового</t>
+          <t>Бездонная поступь часового</t>
         </is>
       </c>
     </row>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Кроваво-огненные ножные щитки опустошителя</t>
+          <t>Кроваво-огненные поножи разорителя</t>
         </is>
       </c>
     </row>
@@ -19942,7 +19942,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Рунные охранные поножи</t>
+          <t>Защитные поножи, скованные рунами</t>
         </is>
       </c>
     </row>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Ботинки авангарда, выкованные в углях</t>
+          <t>Угольнокованые сапоги авангарда</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Боевые ботинки из кровавой стали</t>
+          <t>Боевая поступь из кровавой стали</t>
         </is>
       </c>
     </row>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Шагатели охотника, сотканные тенью</t>
+          <t>Шагоходы охотника, тканные тенью</t>
         </is>
       </c>
     </row>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Сабатоны стража, трёпанные бурей</t>
+          <t>Сабатоны стража, гонимого бурей</t>
         </is>
       </c>
     </row>
@@ -20052,7 +20052,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Походные поножи ночной стражи</t>
+          <t>Походные поножи стража ночи</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Ножные щитки налётчика, меченные порчей</t>
+          <t>Наголенники налётчика, меченые порчей</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Боевые топтатели, связанные пеплом</t>
+          <t>Боевые топотуны, скованные пеплом</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Закалённые латные перчатки</t>
+          <t>Закалённые латные рукавицы</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Кованые железные наручи кистей</t>
+          <t>Кованые железные наручи</t>
         </is>
       </c>
     </row>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Крепкие латунные щитки кулаков</t>
+          <t>Прочные латунные кулачные щитки</t>
         </is>
       </c>
     </row>
@@ -20184,7 +20184,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Прочные стальные боевые перчатки</t>
+          <t>Крепкие стальные боевые перчатки</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20206,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Слоёные чешуйчатые латные перчатки</t>
+          <t>Слоёные чешуйчатые рукавицы</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Укреплённые боевые хваты</t>
+          <t>Усиленные боевые хваты</t>
         </is>
       </c>
     </row>
@@ -20250,7 +20250,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Закалённые рукавицы в железной броне</t>
+          <t>Закалённые железные рукавицы</t>
         </is>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Адокованные латные перчатки джаггернаута</t>
+          <t>Адокованные рукавицы джаггернаута</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Роковые хваты из драконьей чешуи</t>
+          <t>Погибельные хваты из драконьей чешуи</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Позолоченные серные щитки кулаков</t>
+          <t>Позолоченные серные кулачные щитки</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Каменоломные адские руки</t>
+          <t>Адские длани камнелома</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Бездонные охранные поручи</t>
+          <t>Бездонные защитные наручи</t>
         </is>
       </c>
     </row>
@@ -20404,7 +20404,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Роковые стальные латные перчатки крепости</t>
+          <t>Рукавицы-вал из роковой стали</t>
         </is>
       </c>
     </row>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Освящённые дробители в адовой броне</t>
+          <t>Освящённые дробители, облачённые адом</t>
         </is>
       </c>
     </row>
@@ -20470,7 +20470,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Узорчатые латные перчатки бастиона</t>
+          <t>Богато украшенные рукавицы бастиона</t>
         </is>
       </c>
     </row>
@@ -20492,7 +20492,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Гравированные железные стражные руки</t>
+          <t>Гравированные железные длани стража</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Латные наручи кистей авангарда</t>
+          <t>Латные наручи авангарда</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Рыцарские чешуйчатые латные перчатки</t>
+          <t>Чешуйчатые рукавицы рыцарской стражи</t>
         </is>
       </c>
     </row>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Боевые перчатки часового</t>
+          <t>Латные перчатки часового</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Укреплённые рукавицы в железной броне</t>
+          <t>Укреплённые железные рукавицы</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Укреплённые щитки кулаков командира</t>
+          <t>Усиленные кулачные щитки командира</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Истёртые хваты послушника</t>
+          <t>Поношенные перчатки послушника</t>
         </is>
       </c>
     </row>
@@ -20668,7 +20668,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Простые перчатки странника</t>
+          <t>Простые перчатки скитальца</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанные обмотки неофита</t>
+          <t>Истрёпанные обмотки неофита</t>
         </is>
       </c>
     </row>
@@ -20756,7 +20756,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Выцветшие латные перчатки следопыта</t>
+          <t>Выцветшие перчатки следопыта</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Протёртые до нитей обмотки кочевника</t>
+          <t>Ветхие обмотки кочевника</t>
         </is>
       </c>
     </row>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Простые наручи кистей искателя приключений</t>
+          <t>Простые накладки искателя приключений</t>
         </is>
       </c>
     </row>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Адово-тканые хваты арканиста</t>
+          <t>Сотканные в аду перчатки тайноведа</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Роковые перчатки драконьей души</t>
+          <t>Перчатки рока из драконьей души</t>
         </is>
       </c>
     </row>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Обмотки оракула теневого пламени</t>
+          <t>Теневые обмотки оракула</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Угольные латные перчатки искателя чар</t>
+          <t>Перчатки заклинателя, скованные углём</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Серафические наручи ночной вуали</t>
+          <t>Серафические наручи завесы ночи</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20932,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Пепельные рукавицы ведьмомага</t>
+          <t>Пепельные рукавицы хексмага</t>
         </is>
       </c>
     </row>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Бездонные наручи кистей рунотворца</t>
+          <t>Бездонные накладки рунотканца</t>
         </is>
       </c>
     </row>
@@ -20976,7 +20976,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Кроваво-огненные поручи архимага</t>
+          <t>Кроваво-огненные наручи архимага</t>
         </is>
       </c>
     </row>
@@ -20998,7 +20998,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Рунные обмотки послушника</t>
+          <t>Обмотки послушника, скованные рунами</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Тлеющие хваты мистика</t>
+          <t>Угольные перчатки мистика</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21042,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Сотканные из духа перчатки порчи</t>
+          <t>Тканные духом перчатки порчи</t>
         </is>
       </c>
     </row>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Поручи блуждающего огонька ночной вуали</t>
+          <t>Наручи блуждающего огня завесы ночи</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Грозовые рукавицы провидца</t>
+          <t>Рукавицы провидца из нити бури</t>
         </is>
       </c>
     </row>
@@ -21108,7 +21108,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Латные перчатки проводника теневого огня</t>
+          <t>Перчатки проводника теневого пламени</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21130,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Пепельно-тканые наручи кистей с сигилом</t>
+          <t>Пепельнотканые накладки сигила</t>
         </is>
       </c>
     </row>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Наручи адепта, связанные с душой</t>
+          <t>Наручи адепта, связанные душой</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Обветренные наручи авангарда</t>
+          <t>Видавшие виды наручи авангарда</t>
         </is>
       </c>
     </row>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Ржавые латные перчатки с пряжкой</t>
+          <t>Тронутые ржавчиной рукавицы с пряжками</t>
         </is>
       </c>
     </row>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Грубо сработанные поручи рейнджера</t>
+          <t>Грубо литые наручи рейнджера</t>
         </is>
       </c>
     </row>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Закалённые наручи кистей дозорного</t>
+          <t>Закалённые накладки дозорного</t>
         </is>
       </c>
     </row>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Сшитые наручи кистей путника</t>
+          <t>Сшитые накладки странника</t>
         </is>
       </c>
     </row>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Адокованные роковые хваты</t>
+          <t>Адокованные перчатки рока</t>
         </is>
       </c>
     </row>
@@ -21394,7 +21394,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Латные перчатки стража угольной ярости</t>
+          <t>Рукавицы стража угольной ярости</t>
         </is>
       </c>
     </row>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Властелинские перчатки погибели теней</t>
+          <t>Перчатки властелина погибели тьмы</t>
         </is>
       </c>
     </row>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Кроваво-огненные поручи стража порчи</t>
+          <t>Кроваво-огненные наручи хексстража</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21482,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Выкованные в бездне наручи вала</t>
+          <t>Адокованные наручи вала</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Пепельнорождённые наручи кистей джаггернаута</t>
+          <t>Пепельнорождённые накладки джаггернаута</t>
         </is>
       </c>
     </row>
@@ -21526,7 +21526,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Выкованные в углях хваты авангарда</t>
+          <t>Угольнокованые перчатки авангарда</t>
         </is>
       </c>
     </row>
@@ -21548,7 +21548,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Рунные латные перчатки стража обороны</t>
+          <t>Рукавицы стража, скованные рунами</t>
         </is>
       </c>
     </row>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Боевые поручи погибели ночи</t>
+          <t>Боевые наручи погибели ночи</t>
         </is>
       </c>
     </row>
@@ -21592,7 +21592,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Теневобронные обмотки искателя</t>
+          <t>Теневые латные обмотки искателя</t>
         </is>
       </c>
     </row>
@@ -21614,7 +21614,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Грозово-тканые наручи стража</t>
+          <t>Наручи стража, тканные бурей</t>
         </is>
       </c>
     </row>
@@ -21658,7 +21658,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Пепельные рукавицы вала</t>
+          <t>Рукавицы вала, скованные пеплом</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Железновуальные наручи кистей часового</t>
+          <t>Накладки часового железной завесы</t>
         </is>
       </c>
     </row>
@@ -21702,7 +21702,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Истёртый железный боевой шлем</t>
+          <t>Поношенный железный боевой шлем</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Ржавое забрало бастиона</t>
+          <t>Ржавое забрало оплота</t>
         </is>
       </c>
     </row>
@@ -21746,7 +21746,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Побитая стальная защитная каска</t>
+          <t>Побитый стальной шлем стража</t>
         </is>
       </c>
     </row>
@@ -21790,7 +21790,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Потёртая железнобронная каска</t>
+          <t>Потёртый железный шлем</t>
         </is>
       </c>
     </row>
@@ -21856,7 +21856,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Стальная маска часового в выщербинах</t>
+          <t>Изъязвлённая стальная маска часового</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21900,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Роковой шлем из драконьей чешуи</t>
+          <t>Шлем рока из драконьей чешуи</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Бездонный властелинский шлем</t>
+          <t>Бездонный шлем властелина</t>
         </is>
       </c>
     </row>
@@ -21944,7 +21944,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Позолоченная личина преисподней</t>
+          <t>Позолоченный лик преисподней</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Щиток вала королевской позолоты</t>
+          <t>Лицевой щит вала королевской позолоты</t>
         </is>
       </c>
     </row>
@@ -22076,7 +22076,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Теневокованая маска наблюдателя</t>
+          <t>Теневокованая маска дозорного</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Латунный шлем часового</t>
+          <t>Шлем часового, окованный латунью</t>
         </is>
       </c>
     </row>
@@ -22120,7 +22120,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Железный капюшон сумеречного дозора</t>
+          <t>Железный капюшон сумеречной стражи</t>
         </is>
       </c>
     </row>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Боевая личина с угольным кольцом</t>
+          <t>Боевой лик угольного кольца</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Шлем бастиона ночной стражи</t>
+          <t>Шлем бастиона стража ночи</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Боевое забрало из вороненой стали</t>
+          <t>Боевое забрало вороной стали</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22208,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Щиток авангарда с золотой полосой</t>
+          <t>Лицевой щит авангарда с золотой каймой</t>
         </is>
       </c>
     </row>
@@ -22230,7 +22230,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Обветренный капюшон путешественника</t>
+          <t>Видавший виды капюшон путника</t>
         </is>
       </c>
     </row>
@@ -22252,7 +22252,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанная колдовская шляпа</t>
+          <t>Истрёпанная ведьмовская шляпа</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22274,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Запылённый куколь странника</t>
+          <t>Запылённый клобук скитальца</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Истрёпанная шляпа чародея</t>
+          <t>Изорванный колпак чародея</t>
         </is>
       </c>
     </row>
@@ -22318,7 +22318,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Обожжённый капюшон теневой вуали</t>
+          <t>Обожжённый капюшон теневой завесы</t>
         </is>
       </c>
     </row>
@@ -22340,7 +22340,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Простая головная повязка арканиста</t>
+          <t>Простая повязка тайноведа</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Выцветшая шляпа путника</t>
+          <t>Выцветшая шляпа странника</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Инфернальная властелинская диадема</t>
+          <t>Адская диадема властелина</t>
         </is>
       </c>
     </row>
@@ -22428,7 +22428,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Проклятая корона владычества</t>
+          <t>Корона владычества, скованная порчей</t>
         </is>
       </c>
     </row>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Угольно-сплавленный венец оракула</t>
+          <t>Угольный венец оракула</t>
         </is>
       </c>
     </row>
@@ -22472,7 +22472,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Серафический коронет сумерек</t>
+          <t>Серафический венец сумерек</t>
         </is>
       </c>
     </row>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Роковой аркановый нимб</t>
+          <t>Тайный нимб, кованный роком</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22538,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Пепельноблагословлённая диадема мистика</t>
+          <t>Диадема мистика, благословлённая углём</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Адово-тканый венец регента</t>
+          <t>Сотканный в аду венец регента</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Капюшон арканы, связанный тенью</t>
+          <t>Капюшон арканы, скованный тенью</t>
         </is>
       </c>
     </row>
@@ -22604,7 +22604,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Рунно-сшитый куколь провидца</t>
+          <t>Клобук провидца, прошитый рунами</t>
         </is>
       </c>
     </row>
@@ -22626,7 +22626,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Тлеющая шляпа мистика</t>
+          <t>Шляпа мистика из угольной нити</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Сотканная из духа вуаль адепта</t>
+          <t>Тканная духом вуаль адепта</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Капюшон странника, меченный порчей</t>
+          <t>Капюшон скитальца, меченный порчей</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Мантия арканиста ночной вуали</t>
+          <t>Мантия арканиста завесы ночи</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Тронутая грозой колдовская шапка</t>
+          <t>Колпак чар, тронутый бурей</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Сумеречная головная повязка загадки</t>
+          <t>Сумеречная повязка тайны</t>
         </is>
       </c>
     </row>
@@ -22758,7 +22758,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Истёртый капюшон путешественника</t>
+          <t>Поношенный капюшон путника</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22780,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Запылённый куколь рейнджера</t>
+          <t>Запылённый клобук рейнджера</t>
         </is>
       </c>
     </row>
@@ -22802,7 +22802,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Простая повязка разбойника</t>
+          <t>Простая повязка разбойника с большой дороги</t>
         </is>
       </c>
     </row>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Обтрёпанная маска разведчика</t>
+          <t>Истрёпанная маска разведчика</t>
         </is>
       </c>
     </row>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Грубо спрядённый капюшон вестового</t>
+          <t>Грубая холщовая шапка дозорного</t>
         </is>
       </c>
     </row>
@@ -22890,7 +22890,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Протёртый до нитей куколь путника</t>
+          <t>Ветхий клобук странника</t>
         </is>
       </c>
     </row>
@@ -22912,7 +22912,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Закалённая головная повязка странника</t>
+          <t>Закалённая повязка скитальца</t>
         </is>
       </c>
     </row>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Призрачный шлем драконьей души</t>
+          <t>Шлем призрака из драконьей души</t>
         </is>
       </c>
     </row>
@@ -23000,7 +23000,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Угольный боевой куколь</t>
+          <t>Боевой капюшон, скованный углём</t>
         </is>
       </c>
     </row>
@@ -23022,7 +23022,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Черепная личина ночной вуали</t>
+          <t>Череполикая маска завесы ночи</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Шлем хищника пепельной бури</t>
+          <t>Шлем хищника пепельного шторма</t>
         </is>
       </c>
     </row>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Капюшон часового рокового шрама</t>
+          <t>Капюшон часового, меченный роком</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Выкованный в бездне властелинский щиток</t>
+          <t>Адокованный лицевой щит властелина</t>
         </is>
       </c>
     </row>
@@ -23110,7 +23110,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Рунный шлем часового</t>
+          <t>Шлем часового, скованный рунами</t>
         </is>
       </c>
     </row>
@@ -23132,7 +23132,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Выкованная в углях маска вестового</t>
+          <t>Угольнокованая маска дозорного</t>
         </is>
       </c>
     </row>
@@ -23154,7 +23154,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Личина стража теневой вуали</t>
+          <t>Лик стража теневой завесы</t>
         </is>
       </c>
     </row>
@@ -23176,7 +23176,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Железный шлем авангарда</t>
+          <t>Шлем авангарда, окованный железом</t>
         </is>
       </c>
     </row>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Грозоворезной головной щиток наблюдателя</t>
+          <t>Наголовник дозорного, иссечённый бурей</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23242,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Шлем отпрыска ночной стражи</t>
+          <t>Шлем наследника стража ночи</t>
         </is>
       </c>
     </row>
@@ -23264,7 +23264,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Пепельно-тканый щиток искателя</t>
+          <t>Пепельнотканый лицевой щит искателя</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Грубый каменный молот</t>
+          <t>Грубая каменная булава</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Истёртый молоток каменщика</t>
+          <t>Поношенный молот каменщика</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Грубо сработанный боевой молот</t>
+          <t>Грубо отёсанный боевой молот</t>
         </is>
       </c>
     </row>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Покрытая пылью кувалда пилигрима</t>
+          <t>Запылённая кувалда пилигрима</t>
         </is>
       </c>
     </row>
@@ -23396,7 +23396,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Обветренная колотушка налётчика</t>
+          <t>Видавший виды молот налётчика</t>
         </is>
       </c>
     </row>
@@ -23440,7 +23440,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Запятнанный молот глуши</t>
+          <t>Запятнанная булава дикоземья</t>
         </is>
       </c>
     </row>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Катаклизм Адовой кузни</t>
+          <t>Адский катаклизм</t>
         </is>
       </c>
     </row>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Землекрушитель из кровавого осколка</t>
+          <t>Кроваворунный сокрушитель земли</t>
         </is>
       </c>
     </row>
@@ -23506,7 +23506,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Молот руин рокового шпиля</t>
+          <t>Булава гибели роковой башни</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Сокрушитель миров угольной бури</t>
+          <t>Сокрушитель миров угольного шторма</t>
         </is>
       </c>
     </row>
@@ -23550,7 +23550,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Уничтожитель дрожи Пустоты</t>
+          <t>Истребитель пустотной дрожи</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Боевой молот, рассекающий Разлом</t>
+          <t>Боевой молот, рассекающий разломы</t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Череподробитель, связанный злобой</t>
+          <t>Череполом, скованный злобой</t>
         </is>
       </c>
     </row>
@@ -23616,7 +23616,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Клятвопреступный наковальный удар</t>
+          <t>Наковальный удар клятвопреступника</t>
         </is>
       </c>
     </row>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Рунный боевой молот</t>
+          <t>Боевая булава, скованная рунами</t>
         </is>
       </c>
     </row>
@@ -23660,7 +23660,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Выкованная в углях кувалда</t>
+          <t>Угольнокованая кувалда</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23704,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Грозоворезной боевой молот</t>
+          <t>Боевой молот, иссечённый бурей</t>
         </is>
       </c>
     </row>
@@ -23748,7 +23748,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Пепельный дробитель</t>
+          <t>Дробитель, скованный пеплом</t>
         </is>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Роковой молот ночной вуали</t>
+          <t>Булава рока завесы ночи</t>
         </is>
       </c>
     </row>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Железная петля</t>
+          <t>Кольцо, окованное железом</t>
         </is>
       </c>
     </row>
@@ -23836,7 +23836,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Обветренный ободок</t>
+          <t>Видавший виды перстень</t>
         </is>
       </c>
     </row>
@@ -23858,7 +23858,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Потускневшее колечко</t>
+          <t>Потускневший ободок</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Закалённая печатка</t>
+          <t>Закалённый перстень-печатка</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Тусклостальной обруч</t>
+          <t>Кольцо из тусклой стали</t>
         </is>
       </c>
     </row>
@@ -23924,7 +23924,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Истёртое кольцо клятвы</t>
+          <t>Поношенное кольцо клятвы</t>
         </is>
       </c>
     </row>
@@ -23946,7 +23946,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Вычищенное кольцо</t>
+          <t>Истёртый перстень</t>
         </is>
       </c>
     </row>
@@ -23968,7 +23968,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Простокованый ободок</t>
+          <t>Простое кованое кольцо</t>
         </is>
       </c>
     </row>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Роковокованая печатка</t>
+          <t>Печатка, кованная роком</t>
         </is>
       </c>
     </row>
@@ -24012,7 +24012,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Петля адского огня</t>
+          <t>Кольцо адского пламени</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Пустотный ободок</t>
+          <t>Перстень, кованный пустотой</t>
         </is>
       </c>
     </row>
@@ -24122,7 +24122,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Колечко зова смерти</t>
+          <t>Ободок зова смерти</t>
         </is>
       </c>
     </row>
@@ -24166,7 +24166,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Шипастый знак</t>
+          <t>Шипастый сигил</t>
         </is>
       </c>
     </row>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Сумрачнокованый ободок</t>
+          <t>Кольцо мрачной ковки</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24232,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Гравированная рунами петля</t>
+          <t>Кольцо, гравированное рунами</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Колечко мрачного шпиля</t>
+          <t>Ободок мрачной башни</t>
         </is>
       </c>
     </row>
@@ -24298,7 +24298,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Теневопронзающий ободок</t>
+          <t>Кольцо, пронзающее тенью</t>
         </is>
       </c>
     </row>
@@ -24320,7 +24320,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Кольцо, связанное Разломом</t>
+          <t>Кольцо, скованное разломом</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Чародейская ракета</t>
+          <t>Чародейский снаряд</t>
         </is>
       </c>
     </row>
@@ -24406,7 +24406,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Призывает молнию, автоматически наводясь на врагов и нанося {0} урона.</t>
+          <t>Призывает молнию, автоматически нацеливаясь на врагов и нанося {0} урона.</t>
         </is>
       </c>
     </row>
@@ -24472,7 +24472,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Спираль смерти</t>
+          <t>Смертельная спираль</t>
         </is>
       </c>
     </row>
@@ -24495,7 +24495,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>С каждой основной атакой выпускает залп из {2} молотов перед Паладином.
+          <t>С каждой основной атакой выпускает залп из {2} молотов перед паладином.
 Каждый молот наносит {0}% урона основной атаки как {1}.</t>
         </is>
       </c>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Божественный залп</t>
+          <t>Божественный шквал</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Создаёт огненную стену, накладывающую эффект {0} на любого врага, проходящего сквозь неё, и наносящую {1} урона.</t>
+          <t>Создаёт огненную стену, которая накладывает эффект {0} на любого врага, проходящего сквозь неё, нанося {1} урона.</t>
         </is>
       </c>
     </row>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Запускает морозный шар, наносящий {0} урона, охлаждающий врагов и оставляющий ледяной след, который сильно повышает вашу скорость передвижения.</t>
+          <t>Выпускает ледяную сферу, которая наносит {0} урона, накладывает озноб на врагов и оставляет ледяной след, сильно повышающий скорость передвижения.</t>
         </is>
       </c>
     </row>
@@ -24650,7 +24650,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Морозный шар</t>
+          <t>Ледяная сфера</t>
         </is>
       </c>
     </row>
@@ -24694,7 +24694,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Великий молот</t>
+          <t>Молот-громада</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Создаёт {0} вращающихся молотов, расходящихся спиралью от места, где вы стоите, и наносящих {1} урона врагам на их пути.
+          <t xml:space="preserve">Призывает {0} вращающихся молотов, которые по спирали расходятся от места, где вы стоите, нанося {1} урона врагам на своём пути.
 </t>
         </is>
       </c>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Запускает {0} ледяных осколков в ближайшего врага, нанося {1} урона.</t>
+          <t>Выпускает {0} ледяных осколков в ближайшего врага, нанося {1} урона.</t>
         </is>
       </c>
     </row>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>{0} сфер вращаются вокруг вас, нанося {1} урона каждому задетому врагу</t>
+          <t>{0} сфер кружат вокруг вас, нанося {1} урона за каждого задетого врага</t>
         </is>
       </c>
     </row>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>С неба падает метеор, поражая область и нанося всем врагам в ней {0} урона.</t>
+          <t>С неба падает метеор, поражая область и нанося {0} урона всем врагам в ней.</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Когда {0} наносит критический удар по горящему врагу, есть {1} шанс поглотить {2} и нанести {3} дополнительного урона на основе оставшегося урона {2}.</t>
+          <t>Когда {0} наносит критический удар по горящему врагу, с шансом {1} поглощает {2}, нанося {3} дополнительного урона на основе оставшегося урона {2}.</t>
         </is>
       </c>
     </row>
@@ -24916,7 +24916,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Горящий разряд</t>
+          <t>Огненный разряд</t>
         </is>
       </c>
     </row>
@@ -24938,7 +24938,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Когда {0} наносит критический удар, есть {1} шанс выпустить цепь, поражающую {2} врагов с {3} уроном.</t>
+          <t>Когда {0} наносит критический удар, с шансом {1} высвобождает цепь, поражая {2} врагов {3} урона.</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>{0} имеют {1} шанс оглушить задетую цель</t>
+          <t>{0} с шансом {1} оглушают поражённую цель</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Имеет {0} шанс наложить эффект {1} на задетого врага.</t>
+          <t>С шансом {0} накладывает эффект {1} на задетого врага.</t>
         </is>
       </c>
     </row>
@@ -25070,7 +25070,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>{0} разлетается при ударе, замораживая врагов в радиусе {2}м.</t>
+          <t>{0} раскалывается при ударе, замораживая врагов в радиусе {2} м.</t>
         </is>
       </c>
     </row>
@@ -25092,7 +25092,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Крио-нова</t>
+          <t>Криовзрыв</t>
         </is>
       </c>
     </row>
@@ -25114,7 +25114,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Враги, задетые {0}, имеют {1} шанс породить оскверняющую лужу, периодически наносящую урон врагам.</t>
+          <t>Враги, задетые {0}, с шансом {1} порождают разъедающую лужу, которая периодически наносит урон врагам.</t>
         </is>
       </c>
     </row>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Лужа спирали смерти</t>
+          <t>Лужа смертельной спирали</t>
         </is>
       </c>
     </row>
@@ -25158,7 +25158,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>{0} имеет {1} шанс наложить {2} на любого задетого врага.</t>
+          <t>{0} с шансом {1} накладывает {2} на любого задетого врага.</t>
         </is>
       </c>
     </row>
@@ -25180,7 +25180,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Проклятие смерти</t>
+          <t>Смертельное проклятие</t>
         </is>
       </c>
     </row>
@@ -25246,7 +25246,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Когда Огненный шар попадает по врагу с {0}, есть {1} шанс, что он разделится на ещё один огненный шар, который нацелится на случайного ближайшего врага и нанесёт {2} урона.</t>
+          <t>Когда огненный шар попадает по врагу с {0}, с шансом {1} он расщепляется на ещё один огненный шар, который выискивает случайного врага поблизости и наносит {2} урона.</t>
         </is>
       </c>
     </row>
@@ -25268,7 +25268,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Размножение огненных шаров</t>
+          <t>Расщепление огненного шара</t>
         </is>
       </c>
     </row>
@@ -25290,7 +25290,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>{0} теперь образует Кольцо. Ядро пульсирует, периодически притягивая врагов.</t>
+          <t>Теперь {0} образует кольцо. Ядро пульсирует, периодически притягивая врагов.</t>
         </is>
       </c>
     </row>
@@ -25335,7 +25335,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда молот попадает по врагу, есть {1} шанс, что он взорвётся, нанося {2} урона всем ближайшим врагам.
+          <t xml:space="preserve">Когда молот попадает по врагу, с шансом {1} он взрывается, нанося {2} урона всем врагам поблизости.
 </t>
         </is>
       </c>
@@ -25358,7 +25358,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Детонация суда</t>
+          <t>Подрыв возмездия</t>
         </is>
       </c>
     </row>
@@ -25380,7 +25380,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Критические удары основной атакой имеют шанс создать священный луч с небес</t>
+          <t>Критические удары основной атакой с шансом создают святой луч с небес</t>
         </is>
       </c>
     </row>
@@ -25424,7 +25424,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>{0} теперь будет двигаться прочь от вас.</t>
+          <t>Теперь {0} будет удаляться от вас.</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Враги, задетые {0}, имеют {1} шанс породить оскверняющую лужу, периодически наносящую урон врагам.</t>
+          <t>Враги, задетые {0}, с шансом {1} порождают разъедающую лужу, которая периодически наносит урон врагам.</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>{0} теперь накладывают {1} на всех задетых врагов.</t>
+          <t>Теперь {0} накладывают {1} на всех задетых врагов.</t>
         </is>
       </c>
     </row>
@@ -25556,7 +25556,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Метеоры оставляют после удара горящую землю. Любой враг, прошедший по ней, получает эффект {0}.</t>
+          <t>После удара метеоры оставляют горящую землю. Любой враг, проходящий по ней, получает эффект {0}.</t>
         </is>
       </c>
     </row>
@@ -25600,7 +25600,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Подбор пики {0} выпускает {1} шипов наружу, каждый из которых наносит {2} урона и вызывает {3} у врагов</t>
+          <t>Подбор копья {0} выпускает {1} шипов во все стороны, каждый наносит {2} урона и вызывает {3} у врагов</t>
         </is>
       </c>
     </row>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Всплеск шипов</t>
+          <t>Взрыв шипов</t>
         </is>
       </c>
     </row>
@@ -25644,7 +25644,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Высвобождает цепь некротической энергии, перескакивающую между {0} врагами, нанося {1} урона и распространяя {2}.</t>
+          <t>Высвобождает цепь некротической энергии, которая перескакивает между {0} врагами, нанося {1} урона и распространяя {2}.</t>
         </is>
       </c>
     </row>
@@ -25688,7 +25688,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Бросает {0} шипастых цепей во врагов, нанося всем на пути {1} урона.</t>
+          <t>Бросает {0} шипастых цепей во врагов, нанося {1} урона всем на их пути.</t>
         </is>
       </c>
     </row>
@@ -25710,7 +25710,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Пробивающие цепи</t>
+          <t>Пронзающие цепи</t>
         </is>
       </c>
     </row>
@@ -26128,7 +26128,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Длительность активной перегрузки</t>
+          <t>Длительность действия Перегрузки</t>
         </is>
       </c>
     </row>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Бесконечный залп</t>
+          <t>Бесконечный шквал</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Максимальное здоровье</t>
+          <t>Макс. здоровье</t>
         </is>
       </c>
     </row>
@@ -26238,7 +26238,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Растущий кратер</t>
+          <t>Расширяющийся кратер</t>
         </is>
       </c>
     </row>
@@ -26282,7 +26282,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Дополнительная спираль</t>
+          <t>Лишняя спираль</t>
         </is>
       </c>
     </row>
@@ -26326,7 +26326,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Падающий залп</t>
+          <t>Падающий шквал</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Накладывается стаков порчи</t>
+          <t>Накладывается зарядов порчи</t>
         </is>
       </c>
     </row>
@@ -26392,7 +26392,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Повышает скорость и урон Ледяных осколков</t>
+          <t>Повышает скорость и урон ледяных осколков</t>
         </is>
       </c>
     </row>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Больше морозных шаров</t>
+          <t>Больше ледяных сфер</t>
         </is>
       </c>
     </row>
@@ -26502,7 +26502,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Число морозных шаров</t>
+          <t>Число ледяных сфер</t>
         </is>
       </c>
     </row>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает размер Морозных шаров</t>
+          <t>Увеличивает размер ледяных сфер</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Размер морозных шаров</t>
+          <t>Размер ледяных сфер</t>
         </is>
       </c>
     </row>
@@ -26590,7 +26590,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Морозный раскол</t>
+          <t>Ледяной раскол</t>
         </is>
       </c>
     </row>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Урон перегрузки</t>
+          <t>Урон Перегрузки</t>
         </is>
       </c>
     </row>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Удар молотопада</t>
+          <t>Молотобойный удар</t>
         </is>
       </c>
     </row>
@@ -26854,7 +26854,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Грань суда</t>
+          <t>Грань возмездия</t>
         </is>
       </c>
     </row>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Размах суда</t>
+          <t>Длань возмездия</t>
         </is>
       </c>
     </row>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Увеличенные способности</t>
+          <t>Большие способности</t>
         </is>
       </c>
     </row>
@@ -27052,7 +27052,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает длительность Кровотечения</t>
+          <t>Увеличивает длительность кровотечения</t>
         </is>
       </c>
     </row>
@@ -27096,7 +27096,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает длительность Огненной стены</t>
+          <t>Увеличивает длительность огненной стены</t>
         </is>
       </c>
     </row>
@@ -27272,7 +27272,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает число пробитий способности Огненный шар</t>
+          <t>Увеличивает число пробитий способности «Огненный шар»</t>
         </is>
       </c>
     </row>
@@ -27316,7 +27316,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов</t>
+          <t>Кол-во снарядов</t>
         </is>
       </c>
     </row>
@@ -27470,7 +27470,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Неугасающий гром</t>
+          <t>Неутихающий гром</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Пробивающий лёд</t>
+          <t>Пронзающий лёд</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27558,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Пробивающая ракета</t>
+          <t>Пробивающий снаряд</t>
         </is>
       </c>
     </row>
@@ -27646,7 +27646,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Ускоренная смерть</t>
+          <t>Скорая смерть</t>
         </is>
       </c>
     </row>
@@ -27712,7 +27712,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Повышает урон</t>
+          <t>Увеличивает урон</t>
         </is>
       </c>
     </row>
@@ -27756,7 +27756,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов перегрузки</t>
+          <t>Кол-во снарядов Перегрузки</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Быстрые оковы</t>
+          <t>Стремительные оковы</t>
         </is>
       </c>
     </row>
@@ -27844,7 +27844,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает Шипы</t>
+          <t>Увеличивает шипы</t>
         </is>
       </c>
     </row>
@@ -27910,7 +27910,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Тянущиеся цепи</t>
+          <t>Дотягивающиеся цепи</t>
         </is>
       </c>
     </row>
@@ -27976,7 +27976,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Число пробитий перегрузки</t>
+          <t>Число пробитий Перегрузки</t>
         </is>
       </c>
     </row>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Освящённый напор</t>
+          <t>Освящённый натиск</t>
         </is>
       </c>
     </row>
@@ -28020,7 +28020,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Повышает урон</t>
+          <t>Увеличивает урон</t>
         </is>
       </c>
     </row>
@@ -28108,7 +28108,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Добавляет больше снарядов</t>
+          <t>Добавляет снаряды</t>
         </is>
       </c>
     </row>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Залп осколков</t>
+          <t>Шквал осколков</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Запас щита</t>
+          <t>Резерв щита</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Быстрые сферы</t>
+          <t>Стремительные сферы</t>
         </is>
       </c>
     </row>
@@ -28218,7 +28218,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов</t>
+          <t>Кол-во снарядов</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28240,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Дублирование заклинаний</t>
+          <t>Дублирование заклинания</t>
         </is>
       </c>
     </row>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает размер области</t>
+          <t>Увеличивает площадь</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28284,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Распространяющийся гром</t>
+          <t>Расходящийся гром</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28306,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Горение теперь начинается с большего числа стаков</t>
+          <t>Горение теперь начинается с большего числа зарядов</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Восстановление здоровья</t>
+          <t>Сила регенерации здоровья</t>
         </is>
       </c>
     </row>
@@ -28372,7 +28372,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Перезарядка регена</t>
+          <t>Перезарядка регенерации здоровья</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Стойкость</t>
+          <t>Бодрость</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Быстрота</t>
+          <t>Проворство</t>
         </is>
       </c>
     </row>
@@ -28504,7 +28504,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Повышает урон</t>
+          <t>Увеличивает урон</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Вольтовый всплеск</t>
+          <t>Вольтова вспышка</t>
         </is>
       </c>
     </row>
@@ -28592,7 +28592,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Площадь пульса Боевой пики</t>
+          <t>Площадь пульса боевого копья</t>
         </is>
       </c>
     </row>
@@ -28614,7 +28614,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Площадь боевой пики</t>
+          <t>Площадь боевого копья</t>
         </is>
       </c>
     </row>
@@ -28636,7 +28636,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Урон пульса Боевой пики</t>
+          <t>Урон пульса боевого копья</t>
         </is>
       </c>
     </row>
@@ -28658,7 +28658,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Урон боевой пики</t>
+          <t>Урон боевого копья</t>
         </is>
       </c>
     </row>
@@ -28680,7 +28680,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Снаряды подбора Боевой пики</t>
+          <t>Сбор снарядов боевого копья</t>
         </is>
       </c>
     </row>
@@ -28702,7 +28702,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Снаряды боевой пики</t>
+          <t>Снаряды боевого копья</t>
         </is>
       </c>
     </row>
@@ -28768,7 +28768,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Повышает урон</t>
+          <t>Увеличивает урон</t>
         </is>
       </c>
     </row>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Залп Пустоты</t>
+          <t>Залп Бездны</t>
         </is>
       </c>
     </row>
@@ -28834,7 +28834,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Бросает боевую пику, проходящую сквозь врагов и вызывающую {0} у врагов. Пики втыкаются в землю, пульсируя {1} уроном по площади. Воткнутая пика имеет {2} шанс стать подбираемой. Её подбор высвобождает {3} неподбираемых пик.</t>
+          <t>Метает боевое копьё, которое проходит сквозь врагов, нанося {0}. Копья втыкаются в землю, пульсируя и нанося {1} урона по площади. У воткнутого копья есть {2} шанс стать собираемым. Сбор высвобождает {3} несобираемых копий.</t>
         </is>
       </c>
     </row>
@@ -28856,7 +28856,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Боевая пика</t>
+          <t>Боевое копьё</t>
         </is>
       </c>
     </row>
@@ -28878,7 +28878,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Впервые выкуйте мифический предмет.</t>
+          <t>Выкуйте мифический предмет впервые.</t>
         </is>
       </c>
     </row>
@@ -28922,7 +28922,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Попадите {0} снарядами {1} по одному и тому же Боссу за один заброс</t>
+          <t>Попадите {0} снарядами {1} по одному боссу за один каст</t>
         </is>
       </c>
     </row>
@@ -28944,7 +28944,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Зазубренный штурм</t>
+          <t>Шквал шипов</t>
         </is>
       </c>
     </row>
@@ -28966,7 +28966,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов подряд, не получив урона</t>
+          <t>Убейте {0} врагов подряд, не получив ни единого удара</t>
         </is>
       </c>
     </row>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Поразите {0} кровоточащих врагов с помощью {1} за один забег</t>
+          <t>Поразите {0} истекающих кровью врагов с помощью {1} за один забег</t>
         </is>
       </c>
     </row>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Кровная линия</t>
+          <t>Родословная</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Встаньте там, где ночь гуще всего, и выживите.</t>
+          <t>Встаньте там, где ночь гуще всего, — и выживите.</t>
         </is>
       </c>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Нанесите {0} {1} урона за один забег</t>
+          <t>Нанесите {0} урона {1} за один забег</t>
         </is>
       </c>
     </row>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Достигните хотя бы {0} шанса крита перед входом на этап {1}</t>
+          <t>Достигните хотя бы {0} шанса крита до входа на этап {1}</t>
         </is>
       </c>
     </row>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Критический вольтаж</t>
+          <t>Критическое напряжение</t>
         </is>
       </c>
     </row>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Отдайте все свои богатства мёртвым и всё равно одержите верх.</t>
+          <t>Отдайте мёртвым все свои богатства — и всё равно одержите верх.</t>
         </is>
       </c>
     </row>
@@ -29274,7 +29274,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Разрушьте {0} разрушаемых объектов за один забег.</t>
+          <t>Разбейте {0} разрушаемых объектов за один забег.</t>
         </is>
       </c>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Снос III</t>
+          <t>Разрушение III</t>
         </is>
       </c>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Разрушьте {0} разрушаемых объектов за один забег.</t>
+          <t>Разбейте {0} разрушаемых объектов за один забег.</t>
         </is>
       </c>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Снос II</t>
+          <t>Разрушение II</t>
         </is>
       </c>
     </row>
@@ -29362,7 +29362,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Разрушьте {0} разрушаемых объектов за один забег.</t>
+          <t>Разбейте {0} разрушаемых объектов за один забег.</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Снос IV</t>
+          <t>Разрушение IV</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Разрушьте {0} разрушаемых объектов за один забег.</t>
+          <t>Разбейте {0} разрушаемых объектов за один забег.</t>
         </is>
       </c>
     </row>
@@ -29428,7 +29428,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Снос I</t>
+          <t>Разрушение I</t>
         </is>
       </c>
     </row>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Уничтожьте {0} разрушаемых объектов за один забег.</t>
+          <t>Разбейте {0} разрушаемых объектов за один забег.</t>
         </is>
       </c>
     </row>
@@ -29472,7 +29472,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Снос V</t>
+          <t>Разрушение V</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Откройте {0} сундуков, имея меньше {1}% здоровья, в рамках одного этапа</t>
+          <t>Откройте {0} сундуков с уровнем здоровья ниже {1}% за один этап</t>
         </is>
       </c>
     </row>
@@ -29516,7 +29516,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Отчаянное богатство</t>
+          <t>Богатство отчаяния</t>
         </is>
       </c>
     </row>
@@ -29560,7 +29560,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Разрушительный путь</t>
+          <t>Путь разрушения</t>
         </is>
       </c>
     </row>
@@ -29582,7 +29582,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} элитных врагов за один забег, используя перегрузку</t>
+          <t>Убейте {0} элитных врагов за один забег, используя Перегрузку</t>
         </is>
       </c>
     </row>
@@ -29648,7 +29648,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Палач-каратель</t>
+          <t>Палач</t>
         </is>
       </c>
     </row>
@@ -29670,7 +29670,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Победите {0} босса</t>
+          <t>Победите босса {0}</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>В любой момент имейте {0} врагов в пределах {1}м от себя</t>
+          <t>В любой момент удерживайте {0} врагов в радиусе {1} м от себя</t>
         </is>
       </c>
     </row>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Око бури</t>
+          <t>Глаз бури</t>
         </is>
       </c>
     </row>
@@ -29758,7 +29758,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов с помощью {1}, пока активен любой челлендж</t>
+          <t>Убейте {0} врагов с помощью {1}, пока активно любое испытание</t>
         </is>
       </c>
     </row>
@@ -29802,7 +29802,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Во время Коллапса закройте свой первый Разлом.</t>
+          <t>Во время Коллапса запечатайте свой первый Разлом.</t>
         </is>
       </c>
     </row>
@@ -29890,7 +29890,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Соберите {0} золота в сумме.</t>
+          <t>Соберите {0} золота суммарно.</t>
         </is>
       </c>
     </row>
@@ -29912,7 +29912,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Скопидом золота III</t>
+          <t>Скопидом III</t>
         </is>
       </c>
     </row>
@@ -29934,7 +29934,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Соберите {0} золота в сумме.</t>
+          <t>Соберите {0} золота суммарно.</t>
         </is>
       </c>
     </row>
@@ -29956,7 +29956,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Скопидом золота II</t>
+          <t>Скопидом II</t>
         </is>
       </c>
     </row>
@@ -29978,7 +29978,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Соберите {0} золота в сумме.</t>
+          <t>Соберите {0} золота суммарно.</t>
         </is>
       </c>
     </row>
@@ -30000,7 +30000,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Скопидом золота IV</t>
+          <t>Скопидом IV</t>
         </is>
       </c>
     </row>
@@ -30022,7 +30022,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Соберите {0} золота в сумме.</t>
+          <t>Соберите {0} золота суммарно.</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Скопидом золота I</t>
+          <t>Скопидом I</t>
         </is>
       </c>
     </row>
@@ -30286,7 +30286,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Уничтожьте {0} разрушаемых объектов в сумме.</t>
+          <t>Разбейте {0} разрушаемых объектов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30308,7 +30308,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Сокрушитель могил III</t>
+          <t>Крушитель могил III</t>
         </is>
       </c>
     </row>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Уничтожьте {0} разрушаемых объектов в сумме.</t>
+          <t>Разбейте {0} разрушаемых объектов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30352,7 +30352,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Сокрушитель могил II</t>
+          <t>Крушитель могил II</t>
         </is>
       </c>
     </row>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Уничтожьте {0} разрушаемых объектов в сумме.</t>
+          <t>Разбейте {0} разрушаемых объектов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30396,7 +30396,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Сокрушитель могил IV</t>
+          <t>Крушитель могил IV</t>
         </is>
       </c>
     </row>
@@ -30418,7 +30418,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Уничтожьте {0} разрушаемых объектов в сумме.</t>
+          <t>Разбейте {0} разрушаемых объектов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Сокрушитель могил I</t>
+          <t>Крушитель могил I</t>
         </is>
       </c>
     </row>
@@ -30462,7 +30462,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Убейте элиту, имеющую {0}+ стаков {1}</t>
+          <t>Сразите элиту, на которой {0}+ зарядов {1}</t>
         </is>
       </c>
     </row>
@@ -30506,7 +30506,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Завершите любой этап, активировав {0}+ идолов</t>
+          <t>Завершите любой этап, активировав {0}+ Идолов</t>
         </is>
       </c>
     </row>
@@ -30528,7 +30528,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Ученик Ада</t>
+          <t>Адепт ада</t>
         </is>
       </c>
     </row>
@@ -30550,7 +30550,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов в сумме.</t>
+          <t>Сразите {0} врагов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30572,7 +30572,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Жнец орды III</t>
+          <t>Жнец полчищ III</t>
         </is>
       </c>
     </row>
@@ -30594,7 +30594,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов в сумме.</t>
+          <t>Сразите {0} врагов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Жнец орды II</t>
+          <t>Жнец полчищ II</t>
         </is>
       </c>
     </row>
@@ -30638,7 +30638,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов в сумме.</t>
+          <t>Сразите {0} врагов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30660,7 +30660,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Жнец орды IV</t>
+          <t>Жнец полчищ IV</t>
         </is>
       </c>
     </row>
@@ -30682,7 +30682,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов в сумме.</t>
+          <t>Сразите {0} врагов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30704,7 +30704,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Жнец орды I</t>
+          <t>Жнец полчищ I</t>
         </is>
       </c>
     </row>
@@ -30726,7 +30726,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов в сумме.</t>
+          <t>Сразите {0} врагов суммарно.</t>
         </is>
       </c>
     </row>
@@ -30748,7 +30748,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Жнец орды V</t>
+          <t>Жнец полчищ V</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30792,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Жаркая орбита</t>
+          <t>Раскалённая орбита</t>
         </is>
       </c>
     </row>
@@ -30814,7 +30814,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Победите босса {0} без срабатывания перегрузки за весь забег</t>
+          <t>Победите босса {0}, ни разу не задействовав Перегрузку за весь забег</t>
         </is>
       </c>
     </row>
@@ -30858,7 +30858,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Активируйте {0} идолов за один забег</t>
+          <t>Активируйте {0} Идолов за один забег</t>
         </is>
       </c>
     </row>
@@ -30924,7 +30924,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Поджигая катушку</t>
+          <t>Поджигая спираль</t>
         </is>
       </c>
     </row>
@@ -30946,7 +30946,7 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Наполните предмет впервые.</t>
+          <t>Влейте свойства в предмет впервые.</t>
         </is>
       </c>
     </row>
@@ -30968,7 +30968,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Наполнение силой</t>
+          <t>Вливание силы</t>
         </is>
       </c>
     </row>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Получите {0} магического урона за один забег</t>
+          <t>Получите {0} урона магией за один забег</t>
         </is>
       </c>
     </row>
@@ -31034,7 +31034,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Продлите {1} до {0} секунд длительности</t>
+          <t>Продлите {1} до длительности в {0} секунд</t>
         </is>
       </c>
     </row>
@@ -31078,7 +31078,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Откройте сундук, когда чемпион или элита находится в пределах {1}м от вас, при здоровье ниже {0}%</t>
+          <t>Откройте сундук, когда чемпион или элита находится в радиусе {1} м от вас, а ваше здоровье ниже {0}%</t>
         </is>
       </c>
     </row>
@@ -31122,7 +31122,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов за один забег.</t>
+          <t>Сразите {0} врагов за один забег.</t>
         </is>
       </c>
     </row>
@@ -31166,7 +31166,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов за один забег.</t>
+          <t>Сразите {0} врагов за один забег.</t>
         </is>
       </c>
     </row>
@@ -31210,7 +31210,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов за один забег.</t>
+          <t>Сразите {0} врагов за один забег.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов за один забег.</t>
+          <t>Сразите {0} врагов за один забег.</t>
         </is>
       </c>
     </row>
@@ -31298,7 +31298,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} врагов за один забег.</t>
+          <t>Сразите {0} врагов за один забег.</t>
         </is>
       </c>
     </row>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Ночная стража III</t>
+          <t>Ночной дозор III</t>
         </is>
       </c>
     </row>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Ночная стража II</t>
+          <t>Ночной дозор II</t>
         </is>
       </c>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Ночная стража IV</t>
+          <t>Ночной дозор IV</t>
         </is>
       </c>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Ночная стража I</t>
+          <t>Ночной дозор I</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Ночная стража V</t>
+          <t>Ночной дозор V</t>
         </is>
       </c>
     </row>
@@ -31584,7 +31584,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Не уйти</t>
+          <t>Без бегства</t>
         </is>
       </c>
     </row>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} элит в течение {1} секунд друг за другом</t>
+          <t>Убейте {0} элиты в пределах {1} секунд друг от друга</t>
         </is>
       </c>
     </row>
@@ -31628,7 +31628,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Чудо одного удара</t>
+          <t>Убийца с одного удара</t>
         </is>
       </c>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Орбитальная зачистка</t>
+          <t>Орбитальная уборка</t>
         </is>
       </c>
     </row>
@@ -31694,7 +31694,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Закройте {0} Разломов за один Коллапс.</t>
+          <t>Запечатайте {0} Разломов за один Коллапс.</t>
         </is>
       </c>
     </row>
@@ -31716,7 +31716,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Экзорцист овертайма</t>
+          <t>Изгоняющий распад</t>
         </is>
       </c>
     </row>
@@ -31760,7 +31760,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Выкован силой</t>
+          <t>Закалённый силой</t>
         </is>
       </c>
     </row>
@@ -31782,7 +31782,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Завершите весь этап, не восстанавливая здоровье выше {0}%</t>
+          <t>Пройдите целый этап, не восстанавливая здоровье выше {0}%</t>
         </is>
       </c>
     </row>
@@ -31826,7 +31826,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Победите {0} босса</t>
+          <t>Победите босса {0}</t>
         </is>
       </c>
     </row>
@@ -31848,7 +31848,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Царство смерти</t>
+          <t>Власть смерти</t>
         </is>
       </c>
     </row>
@@ -31870,7 +31870,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Закройте {0} Разломов за один Коллапс.</t>
+          <t>Запечатайте {0} Разломов за один Коллапс.</t>
         </is>
       </c>
     </row>
@@ -31914,7 +31914,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Достигните уровня героя {0} за один забег.</t>
+          <t>Достигните {0} уровня героя за один забег.</t>
         </is>
       </c>
     </row>
@@ -31936,7 +31936,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Восходящая сила III</t>
+          <t>Растущая мощь III</t>
         </is>
       </c>
     </row>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Достигните уровня героя {0} за один забег.</t>
+          <t>Достигните {0} уровня героя за один забег.</t>
         </is>
       </c>
     </row>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Восходящая сила II</t>
+          <t>Растущая мощь II</t>
         </is>
       </c>
     </row>
@@ -32002,7 +32002,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Достигните уровня героя {0} за один забег.</t>
+          <t>Достигните {0} уровня героя за один забег.</t>
         </is>
       </c>
     </row>
@@ -32024,7 +32024,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Восходящая сила IV</t>
+          <t>Растущая мощь IV</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Достигните уровня героя {0} за один забег.</t>
+          <t>Достигните {0} уровня героя за один забег.</t>
         </is>
       </c>
     </row>
@@ -32068,7 +32068,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Восходящая сила I</t>
+          <t>Растущая мощь I</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Достигните уровня героя {0} за один забег.</t>
+          <t>Достигните {0} уровня героя за один забег.</t>
         </is>
       </c>
     </row>
@@ -32112,7 +32112,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Восходящая сила V</t>
+          <t>Растущая мощь V</t>
         </is>
       </c>
     </row>
@@ -32134,7 +32134,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Завершите этап, не используя рывок и не опускаясь ниже {0}% здоровья.</t>
+          <t>Пройдите этап без рывков и не опускаясь ниже {0}% здоровья.</t>
         </is>
       </c>
     </row>
@@ -32178,7 +32178,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Захватите {0} рунных камней в сумме.</t>
+          <t>Захватите {0} рунных камней суммарно.</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Захватите {0} рунных камней в сумме.</t>
+          <t>Захватите {0} рунных камней суммарно.</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Захватите {0} рунных камней в сумме.</t>
+          <t>Захватите {0} рунных камней суммарно.</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32310,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Захватите {0} рунных камней в сумме.</t>
+          <t>Захватите {0} рунных камней суммарно.</t>
         </is>
       </c>
     </row>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Захватите {0} рунных камней в сумме.</t>
+          <t>Захватите {0} рунных камней суммарно.</t>
         </is>
       </c>
     </row>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Рунный рывок III</t>
+          <t>Рунная гонка III</t>
         </is>
       </c>
     </row>
@@ -32464,7 +32464,7 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Рунный рывок II</t>
+          <t>Рунная гонка II</t>
         </is>
       </c>
     </row>
@@ -32508,7 +32508,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Рунный рывок IV</t>
+          <t>Рунная гонка IV</t>
         </is>
       </c>
     </row>
@@ -32552,7 +32552,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Рунный рывок I</t>
+          <t>Рунная гонка I</t>
         </is>
       </c>
     </row>
@@ -32596,7 +32596,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Рунный рывок V</t>
+          <t>Рунная гонка V</t>
         </is>
       </c>
     </row>
@@ -32662,7 +32662,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Разберите {0} предметов в сумме.</t>
+          <t>Разберите {0} предметов суммарно.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Мастер лома III</t>
+          <t>Мастер разбора III</t>
         </is>
       </c>
     </row>
@@ -32706,7 +32706,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Разберите {0} предметов в сумме.</t>
+          <t>Разберите {0} предметов суммарно.</t>
         </is>
       </c>
     </row>
@@ -32728,7 +32728,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Мастер лома II</t>
+          <t>Мастер разбора II</t>
         </is>
       </c>
     </row>
@@ -32750,7 +32750,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Разберите {0} предметов в сумме.</t>
+          <t>Разберите {0} предметов суммарно.</t>
         </is>
       </c>
     </row>
@@ -32772,7 +32772,7 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Мастер лома I</t>
+          <t>Мастер разбора I</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Заработайте {0} золота за один этап, не открывая ни одного сундука</t>
+          <t>Заработайте {0} золота за один этап, не открывая сундуков</t>
         </is>
       </c>
     </row>
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Сам себя сделал</t>
+          <t>Всего добился сам</t>
         </is>
       </c>
     </row>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Шок оков</t>
+          <t>Удар оков</t>
         </is>
       </c>
     </row>
@@ -32882,7 +32882,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} скелетов в сумме.</t>
+          <t>Уничтожьте {0} скелетов суммарно.</t>
         </is>
       </c>
     </row>
@@ -32926,7 +32926,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} скелетов в сумме.</t>
+          <t>Уничтожьте {0} скелетов суммарно.</t>
         </is>
       </c>
     </row>
@@ -32970,7 +32970,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} скелетов в сумме.</t>
+          <t>Уничтожьте {0} скелетов суммарно.</t>
         </is>
       </c>
     </row>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Получите {0} уровней в рамках одного этапа</t>
+          <t>Получите {0} уровней за один этап</t>
         </is>
       </c>
     </row>
@@ -33058,7 +33058,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} призраков за один забег, пока открыт Выход.</t>
+          <t>Уничтожьте {0} призраков за один забег, пока открыт выход.</t>
         </is>
       </c>
     </row>
@@ -33102,7 +33102,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} призраков за один забег, пока открыт Выход.</t>
+          <t>Уничтожьте {0} призраков за один забег, пока открыт выход.</t>
         </is>
       </c>
     </row>
@@ -33146,7 +33146,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} призраков за один забег, пока открыт Выход.</t>
+          <t>Уничтожьте {0} призраков за один забег, пока открыт выход.</t>
         </is>
       </c>
     </row>
@@ -33212,7 +33212,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Распространяя чуму</t>
+          <t>Распространение чумы</t>
         </is>
       </c>
     </row>
@@ -33278,7 +33278,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Убейте элиту с {0}+ эффектами</t>
+          <t>Убейте элиту, на которой висит {0}+ статус-эффектов</t>
         </is>
       </c>
     </row>
@@ -33300,7 +33300,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Собиратель эффектов</t>
+          <t>Коллекционер статусов</t>
         </is>
       </c>
     </row>
@@ -33322,7 +33322,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Нанесите {0} урона типа {1} за один забег</t>
+          <t>Нанесите {0} урона {1} за один забег</t>
         </is>
       </c>
     </row>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Преследователь бури</t>
+          <t>Гроза на хвосте</t>
         </is>
       </c>
     </row>
@@ -33388,7 +33388,7 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Грядёт буря</t>
+          <t>Гроза близится</t>
         </is>
       </c>
     </row>
@@ -33410,7 +33410,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Используйте перегрузку {0} раз за один этап</t>
+          <t>Используйте Перегрузку {0} раз за один этап</t>
         </is>
       </c>
     </row>
@@ -33454,7 +33454,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Используйте перегрузку {0} раз за один забег, каждый раз имея меньше {1}% HP</t>
+          <t>Используйте Перегрузку {0} раз за один забег, каждый раз имея меньше {1}% здоровья</t>
         </is>
       </c>
     </row>
@@ -33476,7 +33476,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Выживший на всплеске</t>
+          <t>Переживший всплеск</t>
         </is>
       </c>
     </row>
@@ -33498,7 +33498,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Продержитесь {0} минут в сумме.</t>
+          <t>Продержитесь {0} минут суммарно.</t>
         </is>
       </c>
     </row>
@@ -33520,7 +33520,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Время выжившего III</t>
+          <t>Время выживания III</t>
         </is>
       </c>
     </row>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Продержитесь {0} минут в сумме.</t>
+          <t>Продержитесь {0} минут суммарно.</t>
         </is>
       </c>
     </row>
@@ -33564,7 +33564,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Время выжившего II</t>
+          <t>Время выживания II</t>
         </is>
       </c>
     </row>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Продержитесь {0} минут в сумме.</t>
+          <t>Продержитесь {0} минут суммарно.</t>
         </is>
       </c>
     </row>
@@ -33608,7 +33608,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Время выжившего IV</t>
+          <t>Время выживания IV</t>
         </is>
       </c>
     </row>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Продержитесь {0} минут в сумме.</t>
+          <t>Продержитесь {0} минут суммарно.</t>
         </is>
       </c>
     </row>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Время выжившего I</t>
+          <t>Время выживания I</t>
         </is>
       </c>
     </row>
@@ -33674,7 +33674,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Продержитесь {0} минут в сумме.</t>
+          <t>Продержитесь {0} минут суммарно.</t>
         </is>
       </c>
     </row>
@@ -33696,7 +33696,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Время выжившего V</t>
+          <t>Время выживания V</t>
         </is>
       </c>
     </row>
@@ -33718,7 +33718,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Убейте {0} замороженных врагов</t>
+          <t>Уничтожьте {0} замороженных врагов</t>
         </is>
       </c>
     </row>
@@ -33762,7 +33762,7 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Активируйте все рунные камни, идолов и откройте запертые сундуки за один этап</t>
+          <t>Активируйте все рунные камни и идолы и откройте запертые сундуки за один этап</t>
         </is>
       </c>
     </row>
@@ -33806,7 +33806,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Откройте каждый запертый сундук на всех этапах, прежде чем покинуть этап {0}.</t>
+          <t>Откройте все запертые сундуки на всех этапах до выхода с этапа {0}.</t>
         </is>
       </c>
     </row>
@@ -33850,7 +33850,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Завершите Подсклеп Ранга 3.</t>
+          <t>Пройдите Подсклеп на ранге 3.</t>
         </is>
       </c>
     </row>
@@ -33894,7 +33894,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>Завершите Подсклеп Ранга 2.</t>
+          <t>Пройдите Подсклеп на ранге 2.</t>
         </is>
       </c>
     </row>
@@ -33938,7 +33938,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Завершите Подсклеп Ранга 1.</t>
+          <t>Пройдите Подсклеп на ранге 1.</t>
         </is>
       </c>
     </row>
@@ -34026,7 +34026,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Победите {0} босса, не имея ни одной способности</t>
+          <t>Победите босса {0}, не имея ни одной способности</t>
         </is>
       </c>
     </row>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Захватите все рунные камни на {0} этапах подряд, не покидая зону захвата</t>
+          <t>Захватите все рунные камни на {0} этапах подряд, не покидая зоны захвата</t>
         </is>
       </c>
     </row>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Босс: Гнетущее присутствие</t>
+          <t>Босс: грозное присутствие</t>
         </is>
       </c>
     </row>
@@ -34180,7 +34180,7 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Гарантированный главный аффикс</t>
+          <t>Гарантированный крупный аффикс</t>
         </is>
       </c>
     </row>
@@ -34224,7 +34224,7 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>Великое предложение</t>
+          <t>Великое подношение</t>
         </is>
       </c>
     </row>
@@ -34268,7 +34268,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Босс: Обычное присутствие</t>
+          <t>Босс: обычное присутствие</t>
         </is>
       </c>
     </row>
@@ -34312,7 +34312,7 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Малое предложение</t>
+          <t>Малое подношение</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>Босс: Усиленное присутствие</t>
+          <t>Босс: усиленное присутствие</t>
         </is>
       </c>
     </row>
@@ -34378,7 +34378,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>Шанс на главный аффикс</t>
+          <t>Шанс крупного аффикса</t>
         </is>
       </c>
     </row>
@@ -34422,7 +34422,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Большое предложение</t>
+          <t>Большое подношение</t>
         </is>
       </c>
     </row>
@@ -34488,7 +34488,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Убейте кровавых червей в этой зоне, затем убейте их Королеву</t>
+          <t>Убейте кровавых червей в этой зоне, затем убейте их королеву</t>
         </is>
       </c>
     </row>
@@ -34554,7 +34554,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Кормите Кровавые пилоны, убивая врагов в их области</t>
+          <t>Кормите кровавые пилоны, убивая врагов в их зоне</t>
         </is>
       </c>
     </row>
@@ -34576,7 +34576,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Пилоны крови</t>
+          <t>Кровавые пилоны</t>
         </is>
       </c>
     </row>
@@ -34752,7 +34752,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>Получается за повышение уровня хаоса или за достижения</t>
+          <t>Выпадает при повышении уровня хаоса или за достижения</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>Осколок Хаоса</t>
+          <t>Осколок хаоса</t>
         </is>
       </c>
     </row>
@@ -34796,7 +34796,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>Выпадает из захваченных Разломов</t>
+          <t>Выпадает с захваченных Разломов</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>Камень ужаса</t>
+          <t>Жуткий камень</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       <c r="D477" s="2" t="inlineStr">
         <is>
           <t>Используется для покупки очков в Вечном Древе.
-Выпадает из Разломов, появляющихся после открытия Обелиска.</t>
+Выпадает из Разломов, что появляются после открытия Обелиска.</t>
         </is>
       </c>
     </row>
@@ -34908,7 +34908,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Серый камень</t>
+          <t>Серокамень</t>
         </is>
       </c>
     </row>
@@ -34952,7 +34952,7 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Получается при разборе снаряжения легендарной и выше редкости или при победе над боссами.</t>
+          <t>Производится при разборе легендарного и более редкого снаряжения или при победе над боссами.</t>
         </is>
       </c>
     </row>
@@ -34974,7 +34974,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>Призменный осколок</t>
+          <t>Осколок призмы</t>
         </is>
       </c>
     </row>
@@ -34996,7 +34996,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>Получается при разборе любого снаряжения</t>
+          <t>Производится при разборе любого снаряжения</t>
         </is>
       </c>
     </row>
@@ -35040,7 +35040,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>Грозовое серебро</t>
+          <t>Штормовое серебро</t>
         </is>
       </c>
     </row>
@@ -35062,7 +35062,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Каждый уникальный активный эффект на врагах даёт {0} ко всему урону</t>
+          <t>Каждый уникальный активный статус-эффект на врагах даёт {0} ко всему урону</t>
         </is>
       </c>
     </row>
@@ -35085,7 +35085,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>+{0} к числу снарядов за каждую сработавшую способность.
+          <t>+{0} к кол-ву снарядов за каждую сработавшую способность.
 Длится {1} с</t>
         </is>
       </c>
@@ -35108,7 +35108,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Получаете на {0} больше урона, когда здоровье ниже {1}</t>
+          <t>Получаемый урон выше на {0}, когда здоровье ниже {1}</t>
         </is>
       </c>
     </row>
@@ -35152,7 +35152,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>{0} ко всему урону, пока не получите удар</t>
+          <t>{0} ко всему урону, пока не получен удар</t>
         </is>
       </c>
     </row>
@@ -35196,7 +35196,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>{0} к восстановлению рывка во время боёв с боссами</t>
+          <t>{0} к восстановлению рывка в бою с боссом</t>
         </is>
       </c>
     </row>
@@ -35284,7 +35284,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Критические удары имеют {0} шанс запустить случайную способность</t>
+          <t>Критические удары с шансом {0} вызывают случайную способность</t>
         </is>
       </c>
     </row>
@@ -35416,7 +35416,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>Теряете {0} от макс. здоровья каждые {1} с</t>
+          <t>Теряется {0} макс. здоровья каждые {1} с</t>
         </is>
       </c>
     </row>
@@ -35438,7 +35438,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} от макс. здоровья за убийство</t>
+          <t>Восстанавливает {0} макс. здоровья за убийство</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>Добыча рабочего при сборе</t>
+          <t>Добыча руды рабочими</t>
         </is>
       </c>
     </row>
@@ -35592,7 +35592,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>Скорость рабочего при сборе</t>
+          <t>Скорость добычи руды рабочими</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Каждые {0} убийств без получения урона: {1} к скорости передвижения и атаки (макс. {2} стак(ов))</t>
+          <t>За каждые {0} убийств без урона: {1} к скорости передвижения и атаки (макс. {2} зарядов)</t>
         </is>
       </c>
     </row>
@@ -35880,7 +35880,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} здоровья при активации перегрузки</t>
+          <t>Восстанавливает {0} здоровья при активации Перегрузки</t>
         </is>
       </c>
     </row>
@@ -35924,7 +35924,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Урон перегрузки {0}, но перезарядка {1}</t>
+          <t>Урон Перегрузки {0}, но перезарядка {1}</t>
         </is>
       </c>
     </row>
@@ -35968,7 +35968,7 @@
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>Скорость атаки основного оружия</t>
+          <t>Скорость атаки основным оружием</t>
         </is>
       </c>
     </row>
@@ -36100,7 +36100,7 @@
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} от максимального здоровья</t>
+          <t>Восстанавливает {0} максимального здоровья</t>
         </is>
       </c>
     </row>
@@ -36122,7 +36122,7 @@
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>Ёмкость энергии</t>
+          <t>Запас энергии</t>
         </is>
       </c>
     </row>
@@ -36144,7 +36144,7 @@
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Число снарядов</t>
+          <t>Кол-во снарядов</t>
         </is>
       </c>
     </row>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>Перезарядка регена здоровья</t>
+          <t>Перезарядка регенерации здоровья</t>
         </is>
       </c>
     </row>
@@ -36254,7 +36254,7 @@
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>Запускает все способности при активации перегрузки</t>
+          <t>Вызывает все способности при активации Перегрузки</t>
         </is>
       </c>
     </row>
@@ -36386,7 +36386,7 @@
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>Элитный</t>
+          <t>Элита</t>
         </is>
       </c>
     </row>
@@ -36498,7 +36498,7 @@
       <c r="D552" s="2" t="inlineStr">
         <is>
           <t>{0} к базовому урону
-Весь ваш урон масштабируется от этого значения.</t>
+Весь урон масштабируется от этого значения.</t>
         </is>
       </c>
     </row>
@@ -36520,7 +36520,7 @@
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>Челленджи стоят и дают на {0} больше золота</t>
+          <t>Испытания стоят и дают на {0} больше золота</t>
         </is>
       </c>
     </row>
@@ -36586,7 +36586,7 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>{0} к урону по элитам и боссам</t>
+          <t>{0} урона элитам и боссам</t>
         </is>
       </c>
     </row>
@@ -36676,7 +36676,7 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>{0} к перезарядке регена здоровья</t>
+          <t>{0} к перезарядке регенерации здоровья</t>
         </is>
       </c>
     </row>
@@ -36698,7 +36698,7 @@
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>{0} к пределу магического сопротивления</t>
+          <t>{0} к пределу сопротивления магии</t>
         </is>
       </c>
     </row>
@@ -36720,7 +36720,7 @@
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>{0} к магическому сопротивлению</t>
+          <t>{0} к сопротивлению магии</t>
         </is>
       </c>
     </row>
@@ -36787,8 +36787,8 @@
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>{0} к перезарядке перегрузки
-{1} к урону перегрузки</t>
+          <t>{0} к перезарядке Перегрузки
+{1} к урону Перегрузки</t>
         </is>
       </c>
     </row>
@@ -36832,7 +36832,7 @@
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>{0} к урону эффектов</t>
+          <t>{0} к урону статусов</t>
         </is>
       </c>
     </row>
@@ -36879,10 +36879,10 @@
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>&lt;color=#777&gt;Стиль игры: двигайтесь, чтобы накапливать стаки Засады, затем используйте Рывок, чтобы выпустить ножи.&lt;/color&gt;
-Движение даёт стаки Засады, до {0}. Каждый стак даёт +{1} к уклонению и +{2} к критическому урону.
-Уклонение от атаки даёт +1 стак Засады, до {3} всего. Получение урона снимает {5} стаков Засады.
-Рывок расходует все стаки, метая ножи назад на {4} урона за каждый стак.</t>
+          <t>&lt;color=#777&gt;Стиль игры: двигайтесь, накапливая заряды Засады, затем используйте Рывок, чтобы метнуть ножи.&lt;/color&gt;
+Движение даёт заряды Засады, до {0}. Каждый заряд даёт +{1} к уклонению и +{2} к критическому урону.
+Уклонение от атаки даёт +1 заряд Засады, всего до {3}. Получение урона снимает {5} зарядов Засады.
+Рывок расходует все заряды, метая ножи назад на {4} урона за заряд.</t>
         </is>
       </c>
     </row>
@@ -36904,7 +36904,7 @@
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>Убийца</t>
+          <t>Ассасин</t>
         </is>
       </c>
     </row>
@@ -36926,7 +36926,7 @@
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>Будущая бонусная нода. Увеличивает значение соседних нод.</t>
+          <t>Будущий бонусный узел. Повышает ценность соседних узлов.</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>Каждое завершение челленджа даёт {0} к скорости передвижения до конца этого этапа (сбрасывается на следующем этапе)</t>
+          <t>Каждое завершённое испытание даёт {0} к скорости передвижения до конца этого этапа (сбрасывается на следующем этапе)</t>
         </is>
       </c>
     </row>
@@ -36970,7 +36970,7 @@
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>Напор претендента</t>
+          <t>Натиск претендента</t>
         </is>
       </c>
     </row>
@@ -37014,7 +37014,7 @@
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>Награда из сундуков</t>
+          <t>Богатство сундуков</t>
         </is>
       </c>
     </row>
@@ -37039,10 +37039,10 @@
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>&lt;color=#777&gt;Стиль игры: избегайте урона как можно дольше, чтобы получить прибавку к урону.&lt;/color&gt;
-После {0} с без получения урона вы получаете Фокус (1 стак за {7} с), до {1}.
-Каждый стак Фокуса даёт {2} ко всему урону и {3} к скорости каста.
-Получение урона расходует весь Фокус, выпуская Раскалывающую Нову на {4} урона за стак и накладывая {5}. Вы не можете получать Фокус {6} с.</t>
+          <t>&lt;color=#777&gt;Стиль игры: как можно дольше избегайте урона, чтобы получить прирост урона.&lt;/color&gt;
+После {0} с без получения урона вы получаете Сосредоточение (1 заряд каждые {7} с), до {1}.
+Каждый заряд Сосредоточения даёт {2} ко всему урону и {3} к скорости каста.
+Получение урона расходует всё Сосредоточение, высвобождая Раскалывающий взрыв на {4} урона за заряд и накладывая {5}. Сосредоточение нельзя получать в течение {6} с.</t>
         </is>
       </c>
     </row>
@@ -37064,7 +37064,7 @@
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>Фокус</t>
+          <t>Сосредоточение</t>
         </is>
       </c>
     </row>
@@ -37095,15 +37095,15 @@
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;color=#777&gt;Стиль игры: копите золото до начала Перегрузки, затем быстро тратьте его, выпуская атаки Монетного взрыва.&lt;/color&gt;
+          <t xml:space="preserve">&lt;color=#777&gt;Стиль игры: копите золото до начала Перегрузки, затем быстро тратьте его, высвобождая атаки Монетного залпа.&lt;/color&gt;
 &lt;color=#F2FF8D&gt;&lt;b&gt;Гоблин&lt;/b&gt;&lt;/color&gt;
-&lt;color=#A9A9A9&gt;&lt;b&gt;ПАССИВНЫЕ ТРЕЙТЫ&lt;/b&gt;&lt;/color&gt;
-&lt;color=#777&gt;Стиль игры: копите золото до &lt;color=#F2FF8D&gt;&lt;b&gt;{0}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt;, затем тратьте во время &lt;color=#F2FF8D&gt;&lt;b&gt;Перегрузки&lt;/b&gt;&lt;/color&gt;.&lt;/color&gt;
-Пока ниже &lt;color=#F2FF8D&gt;&lt;b&gt;{0}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt;, вы получаете &lt;color=#F2FF8D&gt;&lt;b&gt;+{1}&lt;/b&gt;&lt;/color&gt; к приросту золота.
-При &lt;color=#F2FF8D&gt;&lt;b&gt;{0}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt; и более вы получаете &lt;color=#F2FF8D&gt;&lt;b&gt;+{2}&lt;/b&gt;&lt;/color&gt; к скорости каста. Во время &lt;color=#F2FF8D&gt;&lt;b&gt;Перегрузки&lt;/b&gt;&lt;/color&gt; основные атаки выпускают &lt;color=#F2FF8D&gt;&lt;b&gt;Монетный взрыв&lt;/b&gt;&lt;/color&gt;, стоящий &lt;color=#F2FF8D&gt;&lt;b&gt;{3}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt; и наносящий &lt;color=#F2FF8D&gt;&lt;b&gt;{4}&lt;/b&gt;&lt;/color&gt; урона.
+&lt;color=#A9A9A9&gt;&lt;b&gt;ПАССИВНЫЕ ЧЕРТЫ&lt;/b&gt;&lt;/color&gt;
+&lt;color=#777&gt;Стиль игры: копите золото до &lt;color=#F2FF8D&gt;&lt;b&gt;{0}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt;, затем тратьте его во время &lt;color=#F2FF8D&gt;&lt;b&gt;Перегрузки&lt;/b&gt;&lt;/color&gt;.&lt;/color&gt;
+Пока у вас меньше &lt;color=#F2FF8D&gt;&lt;b&gt;{0}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt;, вы получаете &lt;color=#F2FF8D&gt;&lt;b&gt;+{1}&lt;/b&gt;&lt;/color&gt; к приросту золота.
+При &lt;color=#F2FF8D&gt;&lt;b&gt;{0}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt; или больше вы получаете &lt;color=#F2FF8D&gt;&lt;b&gt;+{2}&lt;/b&gt;&lt;/color&gt; к скорости каста. Во время &lt;color=#F2FF8D&gt;&lt;b&gt;Перегрузки&lt;/b&gt;&lt;/color&gt; основные атаки выпускают &lt;color=#F2FF8D&gt;&lt;b&gt;Монетный залп&lt;/b&gt;&lt;/color&gt;, стоящий &lt;color=#F2FF8D&gt;&lt;b&gt;{3}&lt;sprite name="Gold"&gt;&lt;/b&gt;&lt;/color&gt; и наносящий &lt;color=#F2FF8D&gt;&lt;b&gt;{4}&lt;/b&gt;&lt;/color&gt; урона.
 &lt;space=0.6em&gt;&lt;color=#333&gt;────────────────────────&lt;/color&gt;&lt;space=0.45em&gt;
 &lt;color=#888&gt;&lt;b&gt;ПРЕДЕЛ ЗОЛОТА&lt;/b&gt;&lt;/color&gt; &lt;color=#777&gt;({5}&lt;sprite name="Gold"&gt;)&lt;/color&gt;
-При максимальной ёмкости подбор золота сокращает &lt;color=#F2FF8D&gt;&lt;b&gt;перезарядку перегрузки&lt;/b&gt;&lt;/color&gt; на &lt;color=#F2FF8D&gt;&lt;b&gt;{6}с&lt;/b&gt;&lt;/color&gt;.
+При максимальном запасе подбор золота снижает &lt;color=#F2FF8D&gt;&lt;b&gt;перезарядку Перегрузки&lt;/b&gt;&lt;/color&gt; на &lt;color=#F2FF8D&gt;&lt;b&gt;{6} с&lt;/b&gt;&lt;/color&gt;.
 </t>
         </is>
       </c>
@@ -37150,9 +37150,9 @@
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>&lt;color=#777&gt;Стиль игры: восполняйте здоровье сверх максимума, чтобы получить буфер, затем врывайтесь во врагов, чтобы получаемые удары высвобождали Ударные волны.&lt;/color&gt;
-Избыточное лечение добавляет Сверхздоровье (до {0} от макс. здоровья).
-Пока у вас есть Сверхздоровье, получение урона высвобождает Ударную волну, нанося {1} урона ближайшим врагам.</t>
+          <t>&lt;color=#777&gt;Стиль игры: лечитесь сверх максимального здоровья, создавая буфер, затем врывайтесь во врагов, чтобы получаемые удары высвобождали Ударные волны.&lt;/color&gt;
+Избыточное лечение даёт Сверхздоровье (до {0} от макс. здоровья). 
+Пока есть Сверхздоровье, получение урона высвобождает Ударную волну, нанося {1} урона ближайшим врагам.</t>
         </is>
       </c>
     </row>
@@ -37196,7 +37196,7 @@
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>На 1-м этапе появляется дополнительный легендарный Сигил</t>
+          <t>На этапе 1 появляется дополнительный легендарный Сигил</t>
         </is>
       </c>
     </row>
@@ -37245,9 +37245,9 @@
       <c r="D584" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;color=#777&gt;Стиль игры: ненадолго остановитесь, чтобы запустить Вакуум, затем стойте на месте, чтобы вызвать Полярность.&lt;/color&gt;
-Постояв на месте &lt;color=#F2FF8D&gt;&lt;b&gt;{0}с&lt;/b&gt;&lt;/color&gt;, вы запускаете &lt;color=#F2FF8D&gt;&lt;b&gt;Вакуум&lt;/b&gt;&lt;/color&gt;.
-Пока &lt;color=#F2FF8D&gt;&lt;b&gt;Вакуум&lt;/b&gt;&lt;/color&gt; активен, радиус сбора увеличивается на &lt;color=#F2FF8D&gt;&lt;b&gt;{1}м&lt;/b&gt;&lt;/color&gt; в секунду. Каждые &lt;color=#F2FF8D&gt;&lt;b&gt;{2}&lt;/b&gt;&lt;/color&gt; собранного опыта призывают сферу, наносящую &lt;color=#F2FF8D&gt;&lt;b&gt;{3}&lt;/b&gt;&lt;/color&gt; в &lt;color=#F2FF8D&gt;&lt;b&gt;{4}м&lt;/b&gt;&lt;/color&gt;.
-После того как &lt;color=#F2FF8D&gt;&lt;b&gt;Вакуум&lt;/b&gt;&lt;/color&gt; длится &lt;color=#F2FF8D&gt;&lt;b&gt;{5}с&lt;/b&gt;&lt;/color&gt;, вы получаете &lt;color=#F2FF8D&gt;&lt;b&gt;Полярность&lt;/b&gt;&lt;/color&gt; на &lt;color=#F2FF8D&gt;&lt;b&gt;{6}с&lt;/b&gt;&lt;/color&gt;, дающую &lt;color=#F2FF8D&gt;&lt;b&gt;{7}&lt;/b&gt;&lt;/color&gt; к числу снарядов &lt;color=#777&gt;(только способности со снарядами)&lt;/color&gt; и &lt;color=#F2FF8D&gt;&lt;b&gt;{8}&lt;/b&gt;&lt;/color&gt; к скорости каста способностей.
+Простояв на месте &lt;color=#F2FF8D&gt;&lt;b&gt;{0} с&lt;/b&gt;&lt;/color&gt;, вы запускаете &lt;color=#F2FF8D&gt;&lt;b&gt;Вакуум&lt;/b&gt;&lt;/color&gt;.
+Пока активен &lt;color=#F2FF8D&gt;&lt;b&gt;Вакуум&lt;/b&gt;&lt;/color&gt;, радиус сбора растёт на &lt;color=#F2FF8D&gt;&lt;b&gt;{1} м&lt;/b&gt;&lt;/color&gt; в секунду. Каждые &lt;color=#F2FF8D&gt;&lt;b&gt;{2}&lt;/b&gt;&lt;/color&gt; собранного опыта призывают сферу, наносящую &lt;color=#F2FF8D&gt;&lt;b&gt;{3}&lt;/b&gt;&lt;/color&gt; в радиусе &lt;color=#F2FF8D&gt;&lt;b&gt;{4} м&lt;/b&gt;&lt;/color&gt;.
+После того как &lt;color=#F2FF8D&gt;&lt;b&gt;Вакуум&lt;/b&gt;&lt;/color&gt; длится &lt;color=#F2FF8D&gt;&lt;b&gt;{5} с&lt;/b&gt;&lt;/color&gt;, вы получаете &lt;color=#F2FF8D&gt;&lt;b&gt;Полярность&lt;/b&gt;&lt;/color&gt; на &lt;color=#F2FF8D&gt;&lt;b&gt;{6} с&lt;/b&gt;&lt;/color&gt;, дающую &lt;color=#F2FF8D&gt;&lt;b&gt;{7}&lt;/b&gt;&lt;/color&gt; к кол-ву снарядов &lt;color=#777&gt;(только способности со снарядами)&lt;/color&gt; и &lt;color=#F2FF8D&gt;&lt;b&gt;{8}&lt;/b&gt;&lt;/color&gt; к скорости каста способностей.
 </t>
         </is>
       </c>
@@ -37314,7 +37314,7 @@
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>Обет Монолита</t>
+          <t>Обещание монолита</t>
         </is>
       </c>
     </row>
@@ -37424,7 +37424,7 @@
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>Захват Рунного камня даёт {0} к радиусу подбора на {1} с</t>
+          <t>Захват Рунного камня даёт {0} к радиусу подбора на {1} секунд</t>
         </is>
       </c>
     </row>
@@ -37578,7 +37578,7 @@
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>Стремительность Сигила</t>
+          <t>Сигильная стремительность</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>Пока активен челлендж, вы получаете {0} к скорости каста способностей</t>
+          <t>Пока активно испытание, вы получаете {0} к скорости каста способностей</t>
         </is>
       </c>
     </row>
@@ -37622,7 +37622,7 @@
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>Фокус испытания</t>
+          <t>Сосредоточение в испытании</t>
         </is>
       </c>
     </row>
@@ -37644,7 +37644,7 @@
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>Каждое завершение челленджа мгновенно восстанавливает {0} здоровья</t>
+          <t>Каждое завершённое испытание мгновенно восстанавливает {0} здоровья</t>
         </is>
       </c>
     </row>
@@ -37710,7 +37710,7 @@
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>Обелиск без Пустоты</t>
+          <t>Обелиск без пустоты</t>
         </is>
       </c>
     </row>
@@ -37820,7 +37820,7 @@
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>Ранг I</t>
+          <t>Уровень I</t>
         </is>
       </c>
     </row>
@@ -37842,7 +37842,7 @@
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>Ранг II</t>
+          <t>Уровень II</t>
         </is>
       </c>
     </row>
@@ -37864,7 +37864,7 @@
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>Ранг III</t>
+          <t>Уровень III</t>
         </is>
       </c>
     </row>
@@ -37886,7 +37886,7 @@
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>Ранг IV</t>
+          <t>Уровень IV</t>
         </is>
       </c>
     </row>
@@ -37930,7 +37930,7 @@
       </c>
       <c r="D615" s="2" t="inlineStr">
         <is>
-          <t>&lt;1&gt;Челленджи&lt;/1&gt; теперь появляются ради дополнительных наград</t>
+          <t>Теперь появляются &lt;1&gt;испытания&lt;/1&gt; ради дополнительных наград</t>
         </is>
       </c>
     </row>
@@ -37952,7 +37952,7 @@
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>Призовите и победите &lt;1&gt;Некроманта&lt;/1&gt;, чтобы завершить этот ранг</t>
+          <t>Призовите и одолейте &lt;1&gt;Некроманта&lt;/1&gt;, чтобы пройти этот уровень</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>Призовите и победите &lt;1&gt;Принца склепа&lt;/1&gt;, чтобы завершить этот ранг</t>
+          <t>Призовите и одолейте &lt;1&gt;Принца склепа&lt;/1&gt;, чтобы пройти этот уровень</t>
         </is>
       </c>
     </row>
@@ -37996,7 +37996,7 @@
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>&lt;1&gt;Идолы&lt;/1&gt; можно активировать, чтобы повысить сложность и награды</t>
+          <t>&lt;1&gt;Идолы&lt;/1&gt; можно активировать ради роста сложности и наград</t>
         </is>
       </c>
     </row>
@@ -38018,7 +38018,7 @@
       </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
-          <t>Теперь может выпадать снаряжение с &lt;1&gt;главными аффиксами&lt;/1&gt;</t>
+          <t>Теперь может выпадать снаряжение с &lt;1&gt;крупными аффиксами&lt;/1&gt;</t>
         </is>
       </c>
     </row>
@@ -38040,7 +38040,7 @@
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>Захватывайте &lt;1&gt;Разломы&lt;/1&gt; во время &lt;1&gt;Коллапса&lt;/1&gt;, чтобы получить ресурсы эндгейма</t>
+          <t>Захватывайте &lt;1&gt;Разломы&lt;/1&gt; во время &lt;1&gt;Коллапса&lt;/1&gt;, чтобы добыть эндгейм-ресурсы</t>
         </is>
       </c>
     </row>
@@ -38062,7 +38062,7 @@
       </c>
       <c r="D621" s="2" t="inlineStr">
         <is>
-          <t>Призовите и победите &lt;1&gt;Палача&lt;/1&gt;, чтобы завершить этот ранг</t>
+          <t>Призовите и одолейте &lt;1&gt;Палача&lt;/1&gt;, чтобы пройти этот уровень</t>
         </is>
       </c>
     </row>
@@ -38084,7 +38084,7 @@
       </c>
       <c r="D622" s="2" t="inlineStr">
         <is>
-          <t>Каждый уникальный активный эффект на врагах даёт {0} ко всему урону</t>
+          <t>Каждый уникальный активный статус-эффект на врагах даёт {0} ко всему урону</t>
         </is>
       </c>
     </row>
@@ -38129,7 +38129,7 @@
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>+{0} к числу снарядов за каждую сработавшую способность.
+          <t>+{0} к кол-ву снарядов за каждую сработавшую способность.
 Длится {1} с</t>
         </is>
       </c>
@@ -38152,7 +38152,7 @@
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>Получаете на {0} больше урона, когда здоровье ниже {1}</t>
+          <t>Получаете на {0} больше урона при здоровье ниже {1}</t>
         </is>
       </c>
     </row>
@@ -38240,7 +38240,7 @@
       </c>
       <c r="D629" s="2" t="inlineStr">
         <is>
-          <t>{0} ко всему урону, пока не получите удар</t>
+          <t>{0} ко всему урону, пока не получен удар</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38284,7 @@
       </c>
       <c r="D631" s="2" t="inlineStr">
         <is>
-          <t>{0} к восстановлению рывка во время боёв с боссами</t>
+          <t>{0} к восстановлению рывка в боях с боссами</t>
         </is>
       </c>
     </row>
@@ -38328,7 +38328,7 @@
       </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
-          <t>Критические удары имеют {0} шанс запустить случайную способность</t>
+          <t>Критические удары с шансом {0} вызывают случайную способность</t>
         </is>
       </c>
     </row>
@@ -38372,7 +38372,7 @@
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>Теряете {0} от макс. здоровья каждые {1} с</t>
+          <t>Теряете {0} макс. здоровья каждые {1} с</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} от макс. здоровья за убийство</t>
+          <t>Восстанавливает {0} макс. здоровья за убийство</t>
         </is>
       </c>
     </row>
@@ -38482,7 +38482,7 @@
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>Железный оберег</t>
+          <t>Железная защита</t>
         </is>
       </c>
     </row>
@@ -38505,8 +38505,8 @@
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>Каждые {0} полученных ударов снимают все бонусы
-{1} к максимальному здоровью</t>
+          <t>Каждый {0}-й полученный удар снимает все бонусы
+{1} к макс. здоровью</t>
         </is>
       </c>
     </row>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="D642" s="2" t="inlineStr">
         <is>
-          <t>Проклятие безумного буйства</t>
+          <t>Проклятие безумного порыва</t>
         </is>
       </c>
     </row>
@@ -38550,7 +38550,7 @@
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>Каждые {0} убийств без получения урона: {1} к скорости передвижения и атаки (макс. {2} стак(ов))</t>
+          <t>За каждые {0} убийств без получения урона: {1} к скорости передвижения и атаки (макс. {2} зарядов)</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="D644" s="2" t="inlineStr">
         <is>
-          <t>Безумное буйство</t>
+          <t>Безумный порыв</t>
         </is>
       </c>
     </row>
@@ -38638,7 +38638,7 @@
       </c>
       <c r="D647" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} здоровья при активации перегрузки</t>
+          <t>Восстанавливает {0} здоровья при активации Перегрузки</t>
         </is>
       </c>
     </row>
@@ -38682,7 +38682,7 @@
       </c>
       <c r="D649" s="2" t="inlineStr">
         <is>
-          <t>Урон перегрузки {0}, но перезарядка {1}</t>
+          <t>Урон Перегрузки {0}, но перезарядка {1}</t>
         </is>
       </c>
     </row>
@@ -38726,7 +38726,7 @@
       </c>
       <c r="D651" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} от максимального здоровья</t>
+          <t>Восстанавливает {0} макс. здоровья</t>
         </is>
       </c>
     </row>
@@ -38792,7 +38792,7 @@
       </c>
       <c r="D654" s="2" t="inlineStr">
         <is>
-          <t>Стремительное возмездие</t>
+          <t>Скорое возмездие</t>
         </is>
       </c>
     </row>
@@ -38814,7 +38814,7 @@
       </c>
       <c r="D655" s="2" t="inlineStr">
         <is>
-          <t>Запускает все способности при активации перегрузки</t>
+          <t>Вызывает все способности при активации Перегрузки</t>
         </is>
       </c>
     </row>
@@ -38858,7 +38858,7 @@
       </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
-          <t>{0} к максимальному здоровью</t>
+          <t>{0} к макс. здоровью</t>
         </is>
       </c>
     </row>
@@ -38880,7 +38880,7 @@
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>Проклятие нестабильного фокуса</t>
+          <t>Проклятие нестабильного сосредоточения</t>
         </is>
       </c>
     </row>
@@ -38924,7 +38924,7 @@
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>Нестабильный фокус</t>
+          <t>Нестабильное сосредоточение</t>
         </is>
       </c>
     </row>
@@ -39100,7 +39100,7 @@
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>Не определён</t>
+          <t>Не определено</t>
         </is>
       </c>
     </row>
@@ -39122,7 +39122,7 @@
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>Наложение {0} на врага с {1} наносит {2} {3} урона за каждый стак {1}.</t>
+          <t>Наложение {0} на врага с {1} наносит {2} {3} урона за каждый заряд {1}.</t>
         </is>
       </c>
     </row>
@@ -39166,7 +39166,7 @@
       </c>
       <c r="D671" s="2" t="inlineStr">
         <is>
-          <t>Убийство врага с {0}, у которого есть {1}, восстанавливает {2} от вашего макс. здоровья</t>
+          <t>Убийство врага с {1} способностью {0} лечит на {2} вашего макс. здоровья</t>
         </is>
       </c>
     </row>
@@ -39188,7 +39188,7 @@
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Могильная жатва</t>
+          <t>Жатва из могилы</t>
         </is>
       </c>
     </row>
@@ -39210,7 +39210,7 @@
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>Убитые горящие враги с {0} шансом взрываются, нанося {1} урона в радиусе</t>
+          <t>Убитые горящие враги с шансом {0} взрываются, нанося {1} урона по площади</t>
         </is>
       </c>
     </row>
@@ -39343,8 +39343,8 @@
       </c>
       <c r="D679" s="2" t="inlineStr">
         <is>
-          <t>Тайные обереги собираются вокруг Мортензии. Даёт {0} энергощита за каждый уровень Мортензии.
-Максимум {1} стаков.</t>
+          <t>Чародейские обереги собираются вокруг Мортензии. Даёт {0} энергощита за каждый уровень Мортензии.
+Максимум {1} зарядов.</t>
         </is>
       </c>
     </row>
@@ -39366,7 +39366,7 @@
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>Тайный оберег</t>
+          <t>Чародейский оберег</t>
         </is>
       </c>
     </row>
@@ -39389,8 +39389,8 @@
       </c>
       <c r="D681" s="2" t="inlineStr">
         <is>
-          <t>Священный свет укрепляет жизненную силу Торена. Даёт {0} максимального здоровья за каждый уровень Торена.
-Максимум {1} стаков.</t>
+          <t>Священный свет укрепляет жизненную силу Торена. Даёт {0} макс. здоровья за каждый уровень Торена.
+Максимум {1} зарядов.</t>
         </is>
       </c>
     </row>
@@ -39456,7 +39456,7 @@
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>Хранилище осколков Хаоса</t>
+          <t>Тайник с осколками хаоса</t>
         </is>
       </c>
     </row>
@@ -39478,7 +39478,7 @@
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>Душа тёмной эльфийки, бурлящая энергией, — Мортензия.</t>
+          <t>Душа тёмной эльфийки Мортензии, бурлящая энергией.</t>
         </is>
       </c>
     </row>
@@ -39522,7 +39522,7 @@
       </c>
       <c r="D687" s="2" t="inlineStr">
         <is>
-          <t>Хранилище валюты</t>
+          <t>Тайник с валютой</t>
         </is>
       </c>
     </row>
@@ -39588,7 +39588,7 @@
       </c>
       <c r="D690" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} макс. здоровья при каждом повышении уровня</t>
+          <t>Восполняет {0} макс. здоровья при каждом повышении уровня</t>
         </is>
       </c>
     </row>
@@ -39632,7 +39632,7 @@
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>Наносит на {0} больше урона врагам с запасом здоровья ниже {1}</t>
+          <t>Наносит на {0} больше урона врагам со здоровьем ниже {1}</t>
         </is>
       </c>
     </row>
@@ -39698,7 +39698,7 @@
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>Дополнительный шаг</t>
+          <t>Лишний шаг</t>
         </is>
       </c>
     </row>
@@ -39764,7 +39764,7 @@
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>Наносит на {0} больше урона врагам с запасом здоровья выше {1}</t>
+          <t>Наносит на {0} больше урона врагам со здоровьем выше {1}</t>
         </is>
       </c>
     </row>
@@ -39808,7 +39808,7 @@
       </c>
       <c r="D700" s="2" t="inlineStr">
         <is>
-          <t>Враги роняют на {0} больше золота</t>
+          <t>Враги дают на {0} больше золота</t>
         </is>
       </c>
     </row>
@@ -39852,7 +39852,7 @@
       </c>
       <c r="D702" s="2" t="inlineStr">
         <is>
-          <t>Враги в радиусе {0}м замедлены на {1}</t>
+          <t>Враги в пределах {0} м замедлены на {1}</t>
         </is>
       </c>
     </row>
@@ -39896,7 +39896,7 @@
       </c>
       <c r="D704" s="2" t="inlineStr">
         <is>
-          <t>{0} пробитий снарядами</t>
+          <t>{0} пробитие снарядов</t>
         </is>
       </c>
     </row>
@@ -39940,7 +39940,7 @@
       </c>
       <c r="D706" s="2" t="inlineStr">
         <is>
-          <t>Враги с шансом {0} появляются со случайным эффектом</t>
+          <t>У врагов есть {0} шанс появиться со случайным статус-эффектом</t>
         </is>
       </c>
     </row>
@@ -39962,7 +39962,7 @@
       </c>
       <c r="D707" s="2" t="inlineStr">
         <is>
-          <t>Заражённое явление</t>
+          <t>Заражённое появление</t>
         </is>
       </c>
     </row>
@@ -39984,7 +39984,7 @@
       </c>
       <c r="D708" s="2" t="inlineStr">
         <is>
-          <t>Все эффекты длятся на {0} дольше</t>
+          <t>Все статус-эффекты длятся на {0} дольше</t>
         </is>
       </c>
     </row>
@@ -40006,7 +40006,7 @@
       </c>
       <c r="D709" s="2" t="inlineStr">
         <is>
-          <t>Затяжная агония</t>
+          <t>Затянувшаяся агония</t>
         </is>
       </c>
     </row>
@@ -40029,8 +40029,8 @@
       </c>
       <c r="D710" s="2" t="inlineStr">
         <is>
-          <t>Однократно предотвращает смерть и вместо этого исцеляет вас до {0} максимального здоровья.
-Максимум один раз за забег.</t>
+          <t>Один раз предотвращает смерть и вместо этого восполняет {0} макс. здоровья.
+Макс. один раз за забег.</t>
         </is>
       </c>
     </row>
@@ -40074,7 +40074,7 @@
       </c>
       <c r="D712" s="2" t="inlineStr">
         <is>
-          <t>Все эффекты имеют {0} макс. стаков</t>
+          <t>У всех статус-эффектов на {0} больше макс. зарядов</t>
         </is>
       </c>
     </row>
@@ -40096,7 +40096,7 @@
       </c>
       <c r="D713" s="2" t="inlineStr">
         <is>
-          <t>Переполнение стека</t>
+          <t>Переполнение зарядов</t>
         </is>
       </c>
     </row>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="D716" s="2" t="inlineStr">
         <is>
-          <t>Становитесь неуязвимы на {0}с после рывка</t>
+          <t>Дарует неуязвимость на {0} с после рывка</t>
         </is>
       </c>
     </row>
@@ -40184,7 +40184,7 @@
       </c>
       <c r="D717" s="2" t="inlineStr">
         <is>
-          <t>Неприкасаемый</t>
+          <t>Неуязвимый</t>
         </is>
       </c>
     </row>
@@ -40250,7 +40250,7 @@
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>Покинутые пределы</t>
+          <t>Покинутый предел</t>
         </is>
       </c>
     </row>
@@ -40294,7 +40294,7 @@
       </c>
       <c r="D722" s="2" t="inlineStr">
         <is>
-          <t>Подсклеп</t>
+          <t>Подземный склеп</t>
         </is>
       </c>
     </row>
@@ -40316,7 +40316,7 @@
       </c>
       <c r="D723" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает шанс крита</t>
+          <t>Повышает шанс крита</t>
         </is>
       </c>
     </row>
@@ -40338,7 +40338,7 @@
       </c>
       <c r="D724" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает холодный урон</t>
+          <t>Повышает холодный урон</t>
         </is>
       </c>
     </row>
@@ -40360,7 +40360,7 @@
       </c>
       <c r="D725" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает некротический урон</t>
+          <t>Повышает некротический урон</t>
         </is>
       </c>
     </row>
@@ -40382,7 +40382,7 @@
       </c>
       <c r="D726" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает некротический урон</t>
+          <t>Повышает некротический урон</t>
         </is>
       </c>
     </row>
@@ -40404,7 +40404,7 @@
       </c>
       <c r="D727" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон кровотечения</t>
+          <t>Повышает урон кровотечения</t>
         </is>
       </c>
     </row>
@@ -40426,7 +40426,7 @@
       </c>
       <c r="D728" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает огненный урон</t>
+          <t>Повышает огненный урон</t>
         </is>
       </c>
     </row>
@@ -40448,7 +40448,7 @@
       </c>
       <c r="D729" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает бонус площади</t>
+          <t>Повышает бонус площади</t>
         </is>
       </c>
     </row>
@@ -40470,7 +40470,7 @@
       </c>
       <c r="D730" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает физический урон</t>
+          <t>Повышает физический урон</t>
         </is>
       </c>
     </row>
@@ -40492,7 +40492,7 @@
       </c>
       <c r="D731" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает физический урон</t>
+          <t>Повышает физический урон</t>
         </is>
       </c>
     </row>
@@ -40514,7 +40514,7 @@
       </c>
       <c r="D732" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает длительность кровотечения</t>
+          <t>Повышает длительность кровотечения</t>
         </is>
       </c>
     </row>
@@ -40536,7 +40536,7 @@
       </c>
       <c r="D733" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон горения</t>
+          <t>Повышает урон горения</t>
         </is>
       </c>
     </row>
@@ -40558,7 +40558,7 @@
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>Увеличивает урон кровотечения</t>
+          <t>Повышает урон кровотечения</t>
         </is>
       </c>
     </row>
@@ -40625,8 +40625,8 @@
       </c>
       <c r="D737" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов площади.
-Встречается на аффиксах снаряжения и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к площади.
+Встречается на аффиксах снаряжения и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40649,8 +40649,8 @@
       </c>
       <c r="D738" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов шанса крита и критического урона.
-Встречается на аффиксах снаряжения и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к шансу крита и критическому урону.
+Встречается на аффиксах снаряжения и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40672,7 +40672,7 @@
       </c>
       <c r="D739" s="2" t="inlineStr">
         <is>
-          <t>Это усиление добавляет вашему билду контроль.</t>
+          <t>Эта сила добавляет контроль в вашу сборку.</t>
         </is>
       </c>
     </row>
@@ -40695,8 +40695,8 @@
       </c>
       <c r="D740" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов урона.
-Встречается на аффиксах снаряжения и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к урону.
+Встречается на аффиксах снаряжения и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40719,8 +40719,8 @@
       </c>
       <c r="D741" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов рывка.
-Встречается на аффиксах снаряжения и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к рывку.
+Встречается на аффиксах снаряжения и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40743,8 +40743,8 @@
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов золота, опыта или подбора.
-Встречается на Вечном Древе, реликвиях и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к золоту, опыту или подбору.
+Встречается в Вечном Древе, на реликвиях и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40766,7 +40766,7 @@
       </c>
       <c r="D743" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от скорости атаки или скорости каста.</t>
+          <t>Эта сила масштабируется от скорости атаки или скорости каста.</t>
         </is>
       </c>
     </row>
@@ -40789,8 +40789,8 @@
       </c>
       <c r="D744" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов скорости передвижения.
-Встречается на аффиксах снаряжения, Вечном Древе и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к скорости передвижения.
+Встречается на аффиксах снаряжения, в Вечном Древе и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40813,8 +40813,8 @@
       </c>
       <c r="D745" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов перегрузки.
-Встречается на аффиксах снаряжения, Вечном Древе и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к Перегрузке.
+Встречается на аффиксах снаряжения, в Вечном Древе и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40837,8 +40837,8 @@
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов числа снарядов.
-Встречается на аффиксах снаряжения и в карточках трейтов во время забега.</t>
+          <t>Эта сила масштабируется от бонусов к кол-ву снарядов.
+Встречается на аффиксах снаряжения и в забеговых картах черт.</t>
         </is>
       </c>
     </row>
@@ -40861,8 +40861,8 @@
       </c>
       <c r="D747" s="2" t="inlineStr">
         <is>
-          <t>Это усиление масштабируется от бонусов урона эффектов.
-Встречается на аффиксах снаряжения и на Вечном Древе.</t>
+          <t>Эта сила масштабируется от бонусов к урону статус-эффектов.
+Встречается на аффиксах снаряжения и в Вечном Древе.</t>
         </is>
       </c>
     </row>
@@ -40884,7 +40884,7 @@
       </c>
       <c r="D748" s="2" t="inlineStr">
         <is>
-          <t>Это усиление повышает вашу выживаемость.</t>
+          <t>Эта сила повышает вашу живучесть.</t>
         </is>
       </c>
     </row>
@@ -40906,7 +40906,7 @@
       </c>
       <c r="D749" s="2" t="inlineStr">
         <is>
-          <t>Превращайте свои способности во время забега в более мощные версии</t>
+          <t>Превращайте свои способности в забеге в более мощную версию</t>
         </is>
       </c>
     </row>
@@ -40951,8 +40951,8 @@
       </c>
       <c r="D751" s="2" t="inlineStr">
         <is>
-          <t>Открывает здание Архива.
-Забирайте выполненные достижения, чтобы получать Осколки Хаоса.</t>
+          <t>Открывает здание «Архив».
+Забирайте завершённые достижения, чтобы получать осколки хаоса.</t>
         </is>
       </c>
     </row>
@@ -41040,7 +41040,7 @@
       </c>
       <c r="D755" s="2" t="inlineStr">
         <is>
-          <t>Позволяет улучшать легендарное снаряжение до мифической редкости, добавляя +1 аффикс на ваш выбор.</t>
+          <t>Позволяет возносить легендарное снаряжение до мифической редкости, добавляя +1 аффикс на ваш выбор.</t>
         </is>
       </c>
     </row>
@@ -41130,7 +41130,7 @@
       </c>
       <c r="D759" s="2" t="inlineStr">
         <is>
-          <t>Челленджи теперь доступны внутри забегов для большей награды.</t>
+          <t>Испытания теперь доступны в забегах ради дополнительных наград.</t>
         </is>
       </c>
     </row>
@@ -41152,7 +41152,7 @@
       </c>
       <c r="D760" s="2" t="inlineStr">
         <is>
-          <t>Челленджи</t>
+          <t>Испытания</t>
         </is>
       </c>
     </row>
@@ -41218,7 +41218,7 @@
       </c>
       <c r="D763" s="2" t="inlineStr">
         <is>
-          <t>Позволяет создавать легендарные предметы у Кузнеца из редкого и обычного снаряжения с главным аффиксом.</t>
+          <t>Позволяет создавать легендарные предметы у Кузнеца из редкого и обычного снаряжения с крупным аффиксом.</t>
         </is>
       </c>
     </row>
@@ -41264,7 +41264,7 @@
       <c r="D765" s="2" t="inlineStr">
         <is>
           <t>Открывает Вечное Древо.
-Сделайте своего персонажа мощнее на гигантском дереве развития.</t>
+Сделайте своего персонажа сильнее на гигантском дереве развития.</t>
         </is>
       </c>
     </row>
@@ -41309,8 +41309,8 @@
       </c>
       <c r="D767" s="2" t="inlineStr">
         <is>
-          <t>Теперь может выпадать снаряжение с главными аффиксами.
-Главные аффиксы значительно увеличивают значение одной характеристики.</t>
+          <t>Теперь может выпадать снаряжение с крупными аффиксами.
+Крупные аффиксы значительно увеличивают значение одной характеристики.</t>
         </is>
       </c>
     </row>
@@ -41332,7 +41332,7 @@
       </c>
       <c r="D768" s="2" t="inlineStr">
         <is>
-          <t>Главные аффиксы</t>
+          <t>Крупные аффиксы</t>
         </is>
       </c>
     </row>
@@ -41354,7 +41354,7 @@
       </c>
       <c r="D769" s="2" t="inlineStr">
         <is>
-          <t>Открывает Мортензию, героиню — тёмную эльфийку, что подчиняет тайную магию своей воле.</t>
+          <t>Открывает Мортензию — героиню, тёмную эльфийку, что подчиняет тайную магию своей воле.</t>
         </is>
       </c>
     </row>
@@ -41508,7 +41508,7 @@
       </c>
       <c r="D776" s="2" t="inlineStr">
         <is>
-          <t>Ранг 1</t>
+          <t>Уровень 1</t>
         </is>
       </c>
     </row>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="D777" s="2" t="inlineStr">
         <is>
-          <t>Призовите и победите Некроманта в Подсклепе ранга II</t>
+          <t>Призовите и одолейте Некроманта в Подсклепье II уровня</t>
         </is>
       </c>
     </row>
@@ -41552,7 +41552,7 @@
       </c>
       <c r="D778" s="2" t="inlineStr">
         <is>
-          <t>Ранг 2</t>
+          <t>Уровень 2</t>
         </is>
       </c>
     </row>
@@ -41574,7 +41574,7 @@
       </c>
       <c r="D779" s="2" t="inlineStr">
         <is>
-          <t>Призовите и победите Принца склепа в Подсклепе ранга III</t>
+          <t>Призовите и одолейте Принца склепа в Подсклепье III уровня</t>
         </is>
       </c>
     </row>
@@ -41596,7 +41596,7 @@
       </c>
       <c r="D780" s="2" t="inlineStr">
         <is>
-          <t>Ранг 3</t>
+          <t>Уровень 3</t>
         </is>
       </c>
     </row>
@@ -41618,7 +41618,7 @@
       </c>
       <c r="D781" s="2" t="inlineStr">
         <is>
-          <t>Призовите и победите Палача в Подсклепе ранга IV</t>
+          <t>Призовите и одолейте Палача в Подсклепье IV уровня</t>
         </is>
       </c>
     </row>
@@ -41640,7 +41640,7 @@
       </c>
       <c r="D782" s="2" t="inlineStr">
         <is>
-          <t>Ранг 4</t>
+          <t>Уровень 4</t>
         </is>
       </c>
     </row>
@@ -41662,7 +41662,7 @@
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>Выполните любое достижение внутри забега.</t>
+          <t>Выполните любое достижение во время забега.</t>
         </is>
       </c>
     </row>
@@ -41684,7 +41684,7 @@
       </c>
       <c r="D784" s="2" t="inlineStr">
         <is>
-          <t>Откройте Кузнеца</t>
+          <t>Разблокируйте Кузнеца</t>
         </is>
       </c>
     </row>
@@ -41706,7 +41706,7 @@
       </c>
       <c r="D785" s="2" t="inlineStr">
         <is>
-          <t>Найдите Камень ужаса</t>
+          <t>Найдите Жуткий камень</t>
         </is>
       </c>
     </row>
@@ -41750,7 +41750,7 @@
       </c>
       <c r="D787" s="2" t="inlineStr">
         <is>
-          <t>Найдите предмет снаряжения с главным аффиксом</t>
+          <t>Найдите предмет снаряжения с крупным аффиксом</t>
         </is>
       </c>
     </row>
@@ -41772,7 +41772,7 @@
       </c>
       <c r="D788" s="2" t="inlineStr">
         <is>
-          <t>Поговорите с «Тенью» в лагере, чтобы открыть новые силы.</t>
+          <t>Поговорите с Тенью в лагере, чтобы открыть новые силы.</t>
         </is>
       </c>
     </row>
@@ -41838,7 +41838,7 @@
       </c>
       <c r="D791" s="2" t="inlineStr">
         <is>
-          <t>Победите в Подсклепе ранга I</t>
+          <t>Победите в Подсклепье I уровня</t>
         </is>
       </c>
     </row>
@@ -41860,7 +41860,7 @@
       </c>
       <c r="D792" s="2" t="inlineStr">
         <is>
-          <t>Победите в Подсклепе ранга II</t>
+          <t>Победите в Подсклепье II уровня</t>
         </is>
       </c>
     </row>
@@ -41882,7 +41882,7 @@
       </c>
       <c r="D793" s="2" t="inlineStr">
         <is>
-          <t>Победите в Подсклепе ранга III</t>
+          <t>Победите в Подсклепье III уровня</t>
         </is>
       </c>
     </row>
@@ -41904,7 +41904,7 @@
       </c>
       <c r="D794" s="2" t="inlineStr">
         <is>
-          <t>Победите в Подсклепе ранга IV</t>
+          <t>Победите в Подсклепье IV уровня</t>
         </is>
       </c>
     </row>
@@ -42300,7 +42300,7 @@
       </c>
       <c r="D812" s="2" t="inlineStr">
         <is>
-          <t>{0} к восстановлению рывка во время боёв с боссами</t>
+          <t>{0} к восстановлению рывка в боях с боссами</t>
         </is>
       </c>
     </row>
@@ -42344,7 +42344,7 @@
       </c>
       <c r="D814" s="2" t="inlineStr">
         <is>
-          <t>Враги с {0}+ разными типами эффектов получают {1} дополнительного урона</t>
+          <t>Враги с {0}+ разными типами статус-эффектов получают {1} дополнительного урона</t>
         </is>
       </c>
     </row>
@@ -42366,7 +42366,7 @@
       </c>
       <c r="D815" s="2" t="inlineStr">
         <is>
-          <t>Сигил мучений</t>
+          <t>Сигил поражения</t>
         </is>
       </c>
     </row>
@@ -42432,7 +42432,7 @@
       </c>
       <c r="D818" s="2" t="inlineStr">
         <is>
-          <t>Агрессивный талисман, добавляющий {0} ко всему урону</t>
+          <t>Агрессивный талисман, добавляет {0} ко всему урону</t>
         </is>
       </c>
     </row>
@@ -42477,8 +42477,8 @@
       </c>
       <c r="D820" s="2" t="inlineStr">
         <is>
-          <t>За каждые {0} собранных кучек золота роняет одну единицу еды {1}.
-Одновременно на земле может лежать до {2} еды от этого эффекта.</t>
+          <t>За каждые {0} собранных кучек золота роняет одну {1} еды.
+На земле может находиться до {2} еды от этого эффекта.</t>
         </is>
       </c>
     </row>
@@ -42500,7 +42500,7 @@
       </c>
       <c r="D821" s="2" t="inlineStr">
         <is>
-          <t>Ложка нищего</t>
+          <t>Ложка попрошайки</t>
         </is>
       </c>
     </row>
@@ -42522,7 +42522,7 @@
       </c>
       <c r="D822" s="2" t="inlineStr">
         <is>
-          <t>Рывок с шансом {2} призывает чёрную дыру в вашей позиции. Она притягивает ближайших врагов, затем взрывается, нанося {1} урона.</t>
+          <t>Рывок с шансом {2} призывает Чёрную дыру на вашей позиции. Она притягивает ближайших врагов, а затем взрывается, нанося {1} урона.</t>
         </is>
       </c>
     </row>
@@ -42654,7 +42654,7 @@
       </c>
       <c r="D828" s="2" t="inlineStr">
         <is>
-          <t>При активации перегрузки запускает все способности</t>
+          <t>Срабатывает всеми способностями при активации Перегрузки</t>
         </is>
       </c>
     </row>
@@ -42698,7 +42698,7 @@
       </c>
       <c r="D830" s="2" t="inlineStr">
         <is>
-          <t>Использование перегрузки замораживает всех врагов вокруг вас</t>
+          <t>Использование Перегрузки замораживает всех врагов вокруг вас</t>
         </is>
       </c>
     </row>
@@ -42786,7 +42786,7 @@
       </c>
       <c r="D834" s="2" t="inlineStr">
         <is>
-          <t>Разрушение объектов выпускает снаряд, нанося врагам {0} {1} урона в радиусе {2}м.</t>
+          <t>Разрушение объектов выпускает снаряд, нанося врагам {0} {1} урона в радиусе {2} м.</t>
         </is>
       </c>
     </row>
@@ -42874,7 +42874,7 @@
       </c>
       <c r="D838" s="2" t="inlineStr">
         <is>
-          <t>Шанс {0} вызвать случайную способность при критическом ударе.</t>
+          <t>{0} шанс сработать случайной способностью при критическом ударе.</t>
         </is>
       </c>
     </row>
@@ -42918,7 +42918,7 @@
       </c>
       <c r="D840" s="2" t="inlineStr">
         <is>
-          <t>Рывок оставляет огненный след, накладывающий +{0} стак {1} на врагов</t>
+          <t>Рывок оставляет огненный след, накладывающий +{0} заряда {1} на врагов</t>
         </is>
       </c>
     </row>
@@ -42962,7 +42962,7 @@
       </c>
       <c r="D842" s="2" t="inlineStr">
         <is>
-          <t>{0} к скорости атаки, пока запас здоровья ниже {1}</t>
+          <t>{0} к скорости атаки, пока здоровье ниже {1}</t>
         </is>
       </c>
     </row>
@@ -43050,7 +43050,7 @@
       </c>
       <c r="D846" s="2" t="inlineStr">
         <is>
-          <t>Сбор золота выпускает снаряд, нанося врагам {0} {1} урона в радиусе {2}м.</t>
+          <t>Сбор золота выпускает снаряд, нанося врагам {0} {1} урона в радиусе {2} м.</t>
         </is>
       </c>
     </row>
@@ -43094,7 +43094,7 @@
       </c>
       <c r="D848" s="2" t="inlineStr">
         <is>
-          <t>Даёт {0} ко всему урону за каждого врага в радиусе {1}м</t>
+          <t>Даёт {0} ко всему урону за каждого врага в радиусе {1} м</t>
         </is>
       </c>
     </row>
@@ -43182,7 +43182,7 @@
       </c>
       <c r="D852" s="2" t="inlineStr">
         <is>
-          <t>Умирающие враги с {3}+ уникальными эффектами взрываются, нанося {0} {1} урона</t>
+          <t>Умирающие враги с {3}+ уникальными статус-эффектами взрываются, нанося {0} {1} урона</t>
         </is>
       </c>
     </row>
@@ -43226,7 +43226,7 @@
       </c>
       <c r="D854" s="2" t="inlineStr">
         <is>
-          <t>Даёт {0} к максимальному здоровью за каждый запертый сундук с сокровищами, который вы открываете после получения этого ключа.</t>
+          <t>Даёт {0} к макс. здоровью за каждый запертый сундук с сокровищами, открытый после получения этого ключа.</t>
         </is>
       </c>
     </row>
@@ -43314,7 +43314,7 @@
       </c>
       <c r="D858" s="2" t="inlineStr">
         <is>
-          <t>Даёт {0} ко всему урону за каждый запертый сундук с сокровищами, который вы открываете после получения этого ключа.</t>
+          <t>Даёт {0} ко всему урону за каждый запертый сундук с сокровищами, открытый после получения этого ключа.</t>
         </is>
       </c>
     </row>
@@ -43358,7 +43358,7 @@
       </c>
       <c r="D860" s="2" t="inlineStr">
         <is>
-          <t>Исцеляет на {0} максимального здоровья при использовании перегрузки</t>
+          <t>Восполняет {0} макс. здоровья при использовании Перегрузки</t>
         </is>
       </c>
     </row>
@@ -43402,7 +43402,7 @@
       </c>
       <c r="D862" s="2" t="inlineStr">
         <is>
-          <t>Защитный талисман, добавляющий {0} к магическому сопротивлению</t>
+          <t>Защитный талисман, добавляет {0} к сопротивлению магии</t>
         </is>
       </c>
     </row>
@@ -43447,8 +43447,8 @@
       </c>
       <c r="D864" s="2" t="inlineStr">
         <is>
-          <t>Отталкивает всех врагов в радиусе {0}м при рывке.
-Враги также оглушаются на {1}с</t>
+          <t>Отталкивает всех врагов в радиусе {0} м при рывке.
+Враги также оглушаются на {1} с</t>
         </is>
       </c>
     </row>
@@ -43470,7 +43470,7 @@
       </c>
       <c r="D865" s="2" t="inlineStr">
         <is>
-          <t>Сапоги импульса</t>
+          <t>Сапоги натиска</t>
         </is>
       </c>
     </row>
@@ -43492,7 +43492,7 @@
       </c>
       <c r="D866" s="2" t="inlineStr">
         <is>
-          <t>При рывке срабатывает случайная способность</t>
+          <t>Срабатывает случайной способностью при рывке</t>
         </is>
       </c>
     </row>
@@ -43514,7 +43514,7 @@
       </c>
       <c r="D867" s="2" t="inlineStr">
         <is>
-          <t>Кнут импульса</t>
+          <t>Хлыст натиска</t>
         </is>
       </c>
     </row>
@@ -43536,7 +43536,7 @@
       </c>
       <c r="D868" s="2" t="inlineStr">
         <is>
-          <t>Даёт {0} к скорости на {1} секунду после рывка</t>
+          <t>Даёт {0} к скорости на {1} секунд после рывка</t>
         </is>
       </c>
     </row>
@@ -43668,7 +43668,7 @@
       </c>
       <c r="D874" s="2" t="inlineStr">
         <is>
-          <t>За каждые {1} врагов, поражённых основной атакой, бьёт молния, нанося {0} {2} урона</t>
+          <t>Каждые {1} врагов, поражённых основной атакой, бьёт молния, нанося {0} {2} урона</t>
         </is>
       </c>
     </row>
@@ -43712,7 +43712,7 @@
       </c>
       <c r="D876" s="2" t="inlineStr">
         <is>
-          <t>Пока перегрузка активна, способности наносят на {0} больше урона</t>
+          <t>Пока активна Перегрузка, способности наносят на {0} больше урона</t>
         </is>
       </c>
     </row>
@@ -43756,7 +43756,7 @@
       </c>
       <c r="D878" s="2" t="inlineStr">
         <is>
-          <t>Восстанавливает {0} максимального здоровья за {1} убийств</t>
+          <t>Восстанавливает {0} максимального здоровья за каждые {1} убийств</t>
         </is>
       </c>
     </row>
@@ -43800,7 +43800,7 @@
       </c>
       <c r="D880" s="2" t="inlineStr">
         <is>
-          <t>{amount:plural:{} Осколок Хаоса|{} Осколка Хаоса|{} Осколков Хаоса}</t>
+          <t>{amount:plural:{} осколок хаоса|{} осколка хаоса|{} осколков хаоса}</t>
         </is>
       </c>
     </row>
@@ -43824,7 +43824,7 @@
       <c r="D881" s="2" t="inlineStr">
         <is>
           <t>Валюта силы. Сохраняется при смерти.
-Получается за повышение Уровня хаоса, захват Разломов и выполнение Достижений.</t>
+Получается за повышение уровня хаоса, захват Разломов и выполнение достижений.</t>
         </is>
       </c>
     </row>
@@ -43846,7 +43846,7 @@
       </c>
       <c r="D882" s="2" t="inlineStr">
         <is>
-          <t>Осколок Хаоса</t>
+          <t>Осколок хаоса</t>
         </is>
       </c>
     </row>
@@ -44000,7 +44000,7 @@
       </c>
       <c r="D889" s="2" t="inlineStr">
         <is>
-          <t>{0} к получению опыта</t>
+          <t>{0} к приросту опыта</t>
         </is>
       </c>
     </row>
@@ -44088,7 +44088,7 @@
       </c>
       <c r="D893" s="2" t="inlineStr">
         <is>
-          <t>{0} к числу снарядов</t>
+          <t>{0} к количеству снарядов</t>
         </is>
       </c>
     </row>
@@ -44178,9 +44178,9 @@
       </c>
       <c r="D897" s="2" t="inlineStr">
         <is>
-          <t>Наносит {0} урона каждые {1}с за стак
-Снижает урон врага на {2} за стак ({6} всего)
-Макс. {3} стаков. Длится [{4}с].</t>
+          <t>Наносит {0} урона каждые {1} с за заряд
+Снижает урон врага на {2} за заряд ({6} всего)
+Макс. {3} зарядов. Длится [{4}s].</t>
         </is>
       </c>
     </row>
@@ -44226,9 +44226,9 @@
       </c>
       <c r="D899" s="2" t="inlineStr">
         <is>
-          <t>Каждый стак увеличивает получаемый урон на +{0} ({4} всего)
-При макс. стаках умирающий враг распространяет +1 стак на других в радиусе {2}м.
-Макс. {1} стаков. Длится {3}с.</t>
+          <t>Каждый заряд повышает получаемый урон на +{0} ({4} всего)
+На макс. зарядах гибнущий враг передаёт +1 заряд другим в радиусе {2} м.
+Макс. {1} зарядов. Длится {3} с.</t>
         </is>
       </c>
     </row>
@@ -44273,8 +44273,8 @@
       </c>
       <c r="D901" s="2" t="inlineStr">
         <is>
-          <t>Наносит {0} урона каждые {1}с за стак
-Макс. {2} стаков. Длится {3}с.</t>
+          <t>Наносит {0} урона каждые {1} с за заряд
+Макс. {2} зарядов. Длится {3} с.</t>
         </is>
       </c>
     </row>
@@ -44318,7 +44318,7 @@
       </c>
       <c r="D903" s="2" t="inlineStr">
         <is>
-          <t>Замедляет передвижение и скорость атаки на {0}. При {1} стаках враг замораживается и не может двигаться.</t>
+          <t>Замедляет передвижение и скорость атаки на {0}. При {1} зарядах враг замораживается и не может двигаться.</t>
         </is>
       </c>
     </row>
@@ -44340,7 +44340,7 @@
       </c>
       <c r="D904" s="2" t="inlineStr">
         <is>
-          <t>Охлаждение</t>
+          <t>Озноб</t>
         </is>
       </c>
     </row>
@@ -44363,8 +44363,8 @@
       </c>
       <c r="D905" s="2" t="inlineStr">
         <is>
-          <t>Убийство врагов роняет заряды. 
-Подберите заряд, чтобы увеличить критический урон на {1} на {2} секунд</t>
+          <t>Убийство врагов выбивает заряды.
+Подбор заряда повышает критический урон на {1} на {2} с.</t>
         </is>
       </c>
     </row>
@@ -44408,7 +44408,7 @@
       </c>
       <c r="D907" s="2" t="inlineStr">
         <is>
-          <t>Накладывает проклятие смерти на врага, заставляя его при гибели взорваться, нанося {0} урона в области {1}м.</t>
+          <t>Накладывает на врага смертельное проклятие: при гибели он взрывается, нанося {0} урона в радиусе {1} м.</t>
         </is>
       </c>
     </row>
@@ -44430,7 +44430,7 @@
       </c>
       <c r="D908" s="2" t="inlineStr">
         <is>
-          <t>Проклятие смерти</t>
+          <t>Смертельное проклятие</t>
         </is>
       </c>
     </row>
@@ -44452,7 +44452,7 @@
       </c>
       <c r="D909" s="2" t="inlineStr">
         <is>
-          <t>Заморозка не даёт врагу двигаться {0} секунд.</t>
+          <t>Заморозка не даёт врагу двигаться в течение {0} с.</t>
         </is>
       </c>
     </row>
@@ -44519,8 +44519,8 @@
       </c>
       <c r="D912" s="2" t="inlineStr">
         <is>
-          <t>Оглушённый враг не может двигаться или действовать {0} секунд.
-Макс. 1 стак.</t>
+          <t>Оглушённый враг не может двигаться или действовать в течение {0} с.
+Макс. 1 заряд.</t>
         </is>
       </c>
     </row>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="D915" s="2" t="inlineStr">
         <is>
-          <t>Скорость снаряда</t>
+          <t>Скорость снарядов</t>
         </is>
       </c>
     </row>
@@ -44652,7 +44652,7 @@
       </c>
       <c r="D918" s="2" t="inlineStr">
         <is>
-          <t>Добыча рабочего при добыче</t>
+          <t>Добыча руды рабочими</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44674,7 @@
       </c>
       <c r="D919" s="2" t="inlineStr">
         <is>
-          <t>Извлекатель</t>
+          <t>Добытчик</t>
         </is>
       </c>
     </row>
@@ -44696,7 +44696,7 @@
       </c>
       <c r="D920" s="2" t="inlineStr">
         <is>
-          <t>Скорость добычи рабочего</t>
+          <t>Скорость добычи руды рабочими</t>
         </is>
       </c>
     </row>
